--- a/Data_Analysis/Sensitivity analysis/BEV/sweep_results_bev_G1.xlsx
+++ b/Data_Analysis/Sensitivity analysis/BEV/sweep_results_bev_G1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,1145 +502,6909 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>322</v>
+        <v>57</v>
       </c>
       <c r="B2" t="n">
-        <v>3241</v>
+        <v>141</v>
       </c>
       <c r="C2" t="n">
-        <v>322</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>47.71297461825204</v>
+        <v>90.01962122273365</v>
       </c>
       <c r="E2" t="n">
-        <v>455.72</v>
+        <v>600</v>
       </c>
       <c r="F2" t="n">
-        <v>161.6158873289232</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G2" t="n">
-        <v>72985.52634566055</v>
+        <v>15852.39968383784</v>
       </c>
       <c r="H2" t="n">
-        <v>-9934.238467891963</v>
+        <v>-310.3213085368962</v>
       </c>
       <c r="I2" t="n">
-        <v>4.555</v>
+        <v>64.36499999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>11.485</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.65</v>
+        <v>-28.615</v>
       </c>
       <c r="L2" t="n">
-        <v>2.355</v>
+        <v>-13.315</v>
       </c>
       <c r="M2" t="n">
-        <v>247.1737965943455</v>
+        <v>110.127759702801</v>
       </c>
       <c r="N2" t="n">
-        <v>7.913161707222892</v>
+        <v>0.9913885025149257</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>322</v>
+        <v>57</v>
       </c>
       <c r="B3" t="n">
-        <v>3242</v>
+        <v>142</v>
       </c>
       <c r="C3" t="n">
-        <v>322</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>46.08227668192797</v>
+        <v>90.01962122273365</v>
       </c>
       <c r="E3" t="n">
-        <v>453.91</v>
+        <v>600</v>
       </c>
       <c r="F3" t="n">
-        <v>162.2603427409329</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G3" t="n">
-        <v>75372.98344159761</v>
+        <v>15852.39968383784</v>
       </c>
       <c r="H3" t="n">
-        <v>-10061.31337515757</v>
+        <v>-310.3213085368962</v>
       </c>
       <c r="I3" t="n">
-        <v>4.53</v>
+        <v>64.36499999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.585</v>
+        <v>-28.615</v>
       </c>
       <c r="L3" t="n">
-        <v>2.29</v>
+        <v>-13.315</v>
       </c>
       <c r="M3" t="n">
-        <v>247.1737969472284</v>
+        <v>110.127759702801</v>
       </c>
       <c r="N3" t="n">
-        <v>7.936311392178908</v>
+        <v>0.9913885025149257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>322</v>
+        <v>57</v>
       </c>
       <c r="B4" t="n">
-        <v>3243</v>
+        <v>143</v>
       </c>
       <c r="C4" t="n">
-        <v>322</v>
+        <v>57</v>
       </c>
       <c r="D4" t="n">
-        <v>48.4242120173468</v>
+        <v>90.01880890437809</v>
       </c>
       <c r="E4" t="n">
-        <v>456.89</v>
+        <v>600</v>
       </c>
       <c r="F4" t="n">
-        <v>161.2020227484446</v>
+        <v>122.7526536225614</v>
       </c>
       <c r="G4" t="n">
-        <v>73443.31079410459</v>
+        <v>15855.36501570203</v>
       </c>
       <c r="H4" t="n">
-        <v>-9864.135528675084</v>
+        <v>-310.7998063293293</v>
       </c>
       <c r="I4" t="n">
-        <v>4.575</v>
+        <v>64.41</v>
       </c>
       <c r="J4" t="n">
-        <v>11.58</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.649999999999999</v>
+        <v>-28.585</v>
       </c>
       <c r="L4" t="n">
-        <v>2.36</v>
+        <v>-13.28</v>
       </c>
       <c r="M4" t="n">
-        <v>242.6084328998986</v>
+        <v>110.0924431797091</v>
       </c>
       <c r="N4" t="n">
-        <v>7.846769612610431</v>
+        <v>1.007945018755676</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="B5" t="n">
-        <v>3244</v>
+        <v>151</v>
       </c>
       <c r="C5" t="n">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
-        <v>46.88798101033034</v>
+        <v>65.11559809244105</v>
       </c>
       <c r="E5" t="n">
-        <v>455.065</v>
+        <v>516.02</v>
       </c>
       <c r="F5" t="n">
-        <v>161.8485099349255</v>
+        <v>142.7301115722973</v>
       </c>
       <c r="G5" t="n">
-        <v>75790.34889605918</v>
+        <v>89975.43359422209</v>
       </c>
       <c r="H5" t="n">
-        <v>-9986.116103236451</v>
+        <v>-6756.72560554433</v>
       </c>
       <c r="I5" t="n">
-        <v>4.55</v>
+        <v>8.56</v>
       </c>
       <c r="J5" t="n">
-        <v>11.31</v>
+        <v>34.225</v>
       </c>
       <c r="K5" t="n">
-        <v>1.585</v>
+        <v>4.455000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>2.295</v>
+        <v>6.315</v>
       </c>
       <c r="M5" t="n">
-        <v>242.6084328999027</v>
+        <v>227.8169410455787</v>
       </c>
       <c r="N5" t="n">
-        <v>7.918119424619969</v>
+        <v>3.053180778080107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="B6" t="n">
-        <v>3245</v>
+        <v>152</v>
       </c>
       <c r="C6" t="n">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="D6" t="n">
-        <v>49.17498151006907</v>
+        <v>65.11297029649324</v>
       </c>
       <c r="E6" t="n">
-        <v>458.095</v>
+        <v>516.015</v>
       </c>
       <c r="F6" t="n">
-        <v>160.7779874775688</v>
+        <v>142.7314945758105</v>
       </c>
       <c r="G6" t="n">
-        <v>73815.57537967904</v>
+        <v>89981.69322833959</v>
       </c>
       <c r="H6" t="n">
-        <v>-9771.499180533739</v>
+        <v>-6756.720202099356</v>
       </c>
       <c r="I6" t="n">
-        <v>4.595</v>
+        <v>8.56</v>
       </c>
       <c r="J6" t="n">
-        <v>11.705</v>
+        <v>34.225</v>
       </c>
       <c r="K6" t="n">
-        <v>1.65</v>
+        <v>4.455000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>2.365</v>
+        <v>6.315</v>
       </c>
       <c r="M6" t="n">
-        <v>238.1128176408108</v>
+        <v>227.8169410455787</v>
       </c>
       <c r="N6" t="n">
-        <v>7.823376473805849</v>
+        <v>3.053180778080107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="B7" t="n">
-        <v>3246</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="D7" t="n">
-        <v>47.67876451800075</v>
+        <v>65.13279957153307</v>
       </c>
       <c r="E7" t="n">
-        <v>456.355</v>
+        <v>515.96</v>
       </c>
       <c r="F7" t="n">
-        <v>161.3910051901192</v>
+        <v>142.7467093835508</v>
       </c>
       <c r="G7" t="n">
-        <v>76209.61564505921</v>
+        <v>89949.4559271124</v>
       </c>
       <c r="H7" t="n">
-        <v>-9880.623166072421</v>
+        <v>-6777.721415252064</v>
       </c>
       <c r="I7" t="n">
-        <v>4.57</v>
+        <v>8.395</v>
       </c>
       <c r="J7" t="n">
-        <v>11.45</v>
+        <v>34.14</v>
       </c>
       <c r="K7" t="n">
-        <v>1.585</v>
+        <v>4.435</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>6.235</v>
       </c>
       <c r="M7" t="n">
-        <v>238.1128176408127</v>
+        <v>227.2332450383901</v>
       </c>
       <c r="N7" t="n">
-        <v>7.907189232523739</v>
+        <v>3.148367506504229</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="B8" t="n">
-        <v>3247</v>
+        <v>154</v>
       </c>
       <c r="C8" t="n">
-        <v>322</v>
+        <v>58</v>
       </c>
       <c r="D8" t="n">
-        <v>47.50250942533923</v>
+        <v>65.13042361331715</v>
       </c>
       <c r="E8" t="n">
-        <v>455.555</v>
+        <v>515.955</v>
       </c>
       <c r="F8" t="n">
-        <v>161.6744238863295</v>
+        <v>142.7480927087379</v>
       </c>
       <c r="G8" t="n">
-        <v>72918.06711286264</v>
+        <v>89955.58211909801</v>
       </c>
       <c r="H8" t="n">
-        <v>-9940.990646754948</v>
+        <v>-6778.403971268978</v>
       </c>
       <c r="I8" t="n">
-        <v>4.55</v>
+        <v>8.395</v>
       </c>
       <c r="J8" t="n">
-        <v>11.45</v>
+        <v>34.14</v>
       </c>
       <c r="K8" t="n">
-        <v>1.645</v>
+        <v>4.435</v>
       </c>
       <c r="L8" t="n">
-        <v>2.35</v>
+        <v>6.235</v>
       </c>
       <c r="M8" t="n">
-        <v>247.3186373409776</v>
+        <v>227.2332450383901</v>
       </c>
       <c r="N8" t="n">
-        <v>7.913047927149658</v>
+        <v>3.148367506504229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="B9" t="n">
-        <v>3286</v>
+        <v>155</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>69.74885464038026</v>
+        <v>65.13673896838186</v>
       </c>
       <c r="E9" t="n">
-        <v>527.955</v>
+        <v>515.84</v>
       </c>
       <c r="F9" t="n">
-        <v>139.5035413501849</v>
+        <v>142.7799165895178</v>
       </c>
       <c r="G9" t="n">
-        <v>78116.00960368689</v>
+        <v>89934.67294753676</v>
       </c>
       <c r="H9" t="n">
-        <v>-6316.372810807036</v>
+        <v>-6769.20687118465</v>
       </c>
       <c r="I9" t="n">
-        <v>7.285</v>
+        <v>8.245000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>34.08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.58</v>
+        <v>4.420000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>6.02</v>
+        <v>6.165000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>191.2487963113122</v>
+        <v>226.5181012274975</v>
       </c>
       <c r="N9" t="n">
-        <v>4.321532882127327</v>
+        <v>3.243549950960793</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="B10" t="n">
-        <v>3287</v>
+        <v>156</v>
       </c>
       <c r="C10" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="D10" t="n">
-        <v>70.05705461106128</v>
+        <v>65.13627380227562</v>
       </c>
       <c r="E10" t="n">
-        <v>529.52</v>
+        <v>515.845</v>
       </c>
       <c r="F10" t="n">
-        <v>139.0912376747561</v>
+        <v>142.7785326474752</v>
       </c>
       <c r="G10" t="n">
-        <v>77275.64291649024</v>
+        <v>89938.33433540569</v>
       </c>
       <c r="H10" t="n">
-        <v>-6253.225053685826</v>
+        <v>-6772.670865221167</v>
       </c>
       <c r="I10" t="n">
-        <v>7.285</v>
+        <v>8.245000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>34.08</v>
       </c>
       <c r="K10" t="n">
-        <v>4.59</v>
+        <v>4.420000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>6.035</v>
+        <v>6.165000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>188.5892504800049</v>
+        <v>226.5181012274975</v>
       </c>
       <c r="N10" t="n">
-        <v>4.321558892399789</v>
+        <v>3.243549950960793</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="B11" t="n">
-        <v>3288</v>
+        <v>161</v>
       </c>
       <c r="C11" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="D11" t="n">
-        <v>70.05705461106128</v>
+        <v>64.20265037577266</v>
       </c>
       <c r="E11" t="n">
-        <v>529.52</v>
+        <v>512.09</v>
       </c>
       <c r="F11" t="n">
-        <v>139.0912376747561</v>
+        <v>143.8254841405551</v>
       </c>
       <c r="G11" t="n">
-        <v>77275.64291649024</v>
+        <v>92268.07659361578</v>
       </c>
       <c r="H11" t="n">
-        <v>-6253.225053685826</v>
+        <v>-6933.217400830443</v>
       </c>
       <c r="I11" t="n">
-        <v>7.285</v>
+        <v>7.935</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>31.525</v>
       </c>
       <c r="K11" t="n">
-        <v>4.59</v>
+        <v>4.18</v>
       </c>
       <c r="L11" t="n">
-        <v>6.035</v>
+        <v>5.84</v>
       </c>
       <c r="M11" t="n">
-        <v>188.5892504800049</v>
+        <v>229.9799574386882</v>
       </c>
       <c r="N11" t="n">
-        <v>4.321558892399789</v>
+        <v>3.411694225073339</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="B12" t="n">
-        <v>3289</v>
+        <v>162</v>
       </c>
       <c r="C12" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>68.67127383456635</v>
+        <v>63.9472891291465</v>
       </c>
       <c r="E12" t="n">
-        <v>522.4300000000001</v>
+        <v>510.88</v>
       </c>
       <c r="F12" t="n">
-        <v>140.9788721427499</v>
+        <v>144.1661293719403</v>
       </c>
       <c r="G12" t="n">
-        <v>80967.78517635015</v>
+        <v>92876.9133676577</v>
       </c>
       <c r="H12" t="n">
-        <v>-6527.309348353092</v>
+        <v>-6957.562811111966</v>
       </c>
       <c r="I12" t="n">
-        <v>7.135</v>
+        <v>7.935</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>31.525</v>
       </c>
       <c r="K12" t="n">
-        <v>4.345</v>
+        <v>4.18</v>
       </c>
       <c r="L12" t="n">
-        <v>5.735</v>
+        <v>5.84</v>
       </c>
       <c r="M12" t="n">
-        <v>195.5793957009875</v>
+        <v>229.9799574386882</v>
       </c>
       <c r="N12" t="n">
-        <v>4.321547192258359</v>
+        <v>3.411694225073339</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="B13" t="n">
-        <v>3290</v>
+        <v>163</v>
       </c>
       <c r="C13" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>68.67127383456635</v>
+        <v>63.85117639793485</v>
       </c>
       <c r="E13" t="n">
-        <v>522.4300000000001</v>
+        <v>511.18</v>
       </c>
       <c r="F13" t="n">
-        <v>140.9788721427499</v>
+        <v>144.0815215257578</v>
       </c>
       <c r="G13" t="n">
-        <v>80967.78517635015</v>
+        <v>93126.85593620023</v>
       </c>
       <c r="H13" t="n">
-        <v>-6527.309348353092</v>
+        <v>-6964.749581238442</v>
       </c>
       <c r="I13" t="n">
-        <v>7.135</v>
+        <v>7.95</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>29.595</v>
       </c>
       <c r="K13" t="n">
-        <v>4.345</v>
+        <v>4.045000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>5.735</v>
+        <v>5.725000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>195.5793957009875</v>
+        <v>234.9730698367608</v>
       </c>
       <c r="N13" t="n">
-        <v>4.321547192258359</v>
+        <v>3.370452634812113</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="B14" t="n">
-        <v>3291</v>
+        <v>164</v>
       </c>
       <c r="C14" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>68.98129174585007</v>
+        <v>63.07793714966666</v>
       </c>
       <c r="E14" t="n">
-        <v>523.86</v>
+        <v>507.985</v>
       </c>
       <c r="F14" t="n">
-        <v>140.5940369059231</v>
+        <v>144.9877302942742</v>
       </c>
       <c r="G14" t="n">
-        <v>80131.58251956655</v>
+        <v>95001.0893670542</v>
       </c>
       <c r="H14" t="n">
-        <v>-6462.247334624341</v>
+        <v>-7086.363242287818</v>
       </c>
       <c r="I14" t="n">
-        <v>7.135</v>
+        <v>7.935</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>29.535</v>
       </c>
       <c r="K14" t="n">
-        <v>4.350000000000001</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>5.745000000000001</v>
+        <v>5.680000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>192.8453458125807</v>
+        <v>234.9744976534789</v>
       </c>
       <c r="N14" t="n">
-        <v>4.321572535064321</v>
+        <v>3.370452634812113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>3292</v>
+        <v>165</v>
       </c>
       <c r="C15" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>68.98129174585007</v>
+        <v>63.83319368941384</v>
       </c>
       <c r="E15" t="n">
-        <v>523.86</v>
+        <v>510.98</v>
       </c>
       <c r="F15" t="n">
-        <v>140.5940369059231</v>
+        <v>144.1379157179085</v>
       </c>
       <c r="G15" t="n">
-        <v>80131.58251956655</v>
+        <v>93171.89733475244</v>
       </c>
       <c r="H15" t="n">
-        <v>-6462.247334624341</v>
+        <v>-6967.850510331727</v>
       </c>
       <c r="I15" t="n">
-        <v>7.135</v>
+        <v>7.805000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>29.505</v>
       </c>
       <c r="K15" t="n">
-        <v>4.350000000000001</v>
+        <v>4.024999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>5.745000000000001</v>
+        <v>5.649999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>192.8453458125807</v>
+        <v>234.1892634475509</v>
       </c>
       <c r="N15" t="n">
-        <v>4.321572535064321</v>
+        <v>3.475141405901498</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="B16" t="n">
-        <v>3293</v>
+        <v>166</v>
       </c>
       <c r="C16" t="n">
-        <v>323</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>69.3210314106506</v>
+        <v>63.07182613838266</v>
       </c>
       <c r="E16" t="n">
-        <v>525.51</v>
+        <v>507.805</v>
       </c>
       <c r="F16" t="n">
-        <v>140.1525987584192</v>
+        <v>145.0391236272523</v>
       </c>
       <c r="G16" t="n">
-        <v>79219.31286562524</v>
+        <v>95021.70025393597</v>
       </c>
       <c r="H16" t="n">
-        <v>-6401.573699439072</v>
+        <v>-7095.876491927684</v>
       </c>
       <c r="I16" t="n">
-        <v>7.140000000000001</v>
+        <v>7.785</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>29.45</v>
       </c>
       <c r="K16" t="n">
-        <v>4.355</v>
+        <v>3.98</v>
       </c>
       <c r="L16" t="n">
-        <v>5.75</v>
+        <v>5.605</v>
       </c>
       <c r="M16" t="n">
-        <v>190.0936661727588</v>
+        <v>234.1892738040166</v>
       </c>
       <c r="N16" t="n">
-        <v>4.32159364778235</v>
+        <v>3.475141405901498</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="B17" t="n">
-        <v>3331</v>
+        <v>171</v>
       </c>
       <c r="C17" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="D17" t="n">
-        <v>59.49085720970372</v>
+        <v>63.75706224298479</v>
       </c>
       <c r="E17" t="n">
-        <v>480.7</v>
+        <v>510.67</v>
       </c>
       <c r="F17" t="n">
-        <v>153.21737502296</v>
+        <v>144.2254140120565</v>
       </c>
       <c r="G17" t="n">
-        <v>82427.4746233732</v>
+        <v>93358.00467667825</v>
       </c>
       <c r="H17" t="n">
-        <v>-8413.0999302132</v>
+        <v>-6973.31268390403</v>
       </c>
       <c r="I17" t="n">
-        <v>5.24</v>
+        <v>7.605</v>
       </c>
       <c r="J17" t="n">
-        <v>18.7</v>
+        <v>28.96</v>
       </c>
       <c r="K17" t="n">
-        <v>2.51</v>
+        <v>4.005</v>
       </c>
       <c r="L17" t="n">
-        <v>3.43</v>
+        <v>5.555</v>
       </c>
       <c r="M17" t="n">
-        <v>224.9750580698667</v>
+        <v>236.4037905344391</v>
       </c>
       <c r="N17" t="n">
-        <v>6.970510206804811</v>
+        <v>3.638509381311929</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="B18" t="n">
-        <v>3332</v>
+        <v>172</v>
       </c>
       <c r="C18" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>59.49085720970372</v>
+        <v>62.73903947241853</v>
       </c>
       <c r="E18" t="n">
-        <v>480.7</v>
+        <v>506.875</v>
       </c>
       <c r="F18" t="n">
-        <v>153.21737502296</v>
+        <v>145.3052373337349</v>
       </c>
       <c r="G18" t="n">
-        <v>85669.64200844093</v>
+        <v>95847.60661556116</v>
       </c>
       <c r="H18" t="n">
-        <v>-8413.0999302132</v>
+        <v>-7158.120174796257</v>
       </c>
       <c r="I18" t="n">
-        <v>5.24</v>
+        <v>7.54</v>
       </c>
       <c r="J18" t="n">
-        <v>18.7</v>
+        <v>27.675</v>
       </c>
       <c r="K18" t="n">
-        <v>2.51</v>
+        <v>3.829999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>3.43</v>
+        <v>5.379999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>224.9750580698667</v>
+        <v>237.4241364295414</v>
       </c>
       <c r="N18" t="n">
-        <v>6.970510206804811</v>
+        <v>3.638509381311929</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="B19" t="n">
-        <v>3333</v>
+        <v>173</v>
       </c>
       <c r="C19" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>60.07681334224453</v>
+        <v>63.7314904978798</v>
       </c>
       <c r="E19" t="n">
-        <v>482.105</v>
+        <v>510.665</v>
       </c>
       <c r="F19" t="n">
-        <v>152.7708531824745</v>
+        <v>144.2268261453925</v>
       </c>
       <c r="G19" t="n">
-        <v>82388.79197475422</v>
+        <v>93426.61620759337</v>
       </c>
       <c r="H19" t="n">
-        <v>-8341.358994065151</v>
+        <v>-6980.004782798668</v>
       </c>
       <c r="I19" t="n">
-        <v>5.205</v>
+        <v>7.49</v>
       </c>
       <c r="J19" t="n">
-        <v>19.23</v>
+        <v>28.845</v>
       </c>
       <c r="K19" t="n">
-        <v>2.505000000000001</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>3.41</v>
+        <v>5.505</v>
       </c>
       <c r="M19" t="n">
-        <v>221.2319672436798</v>
+        <v>236.2312187258296</v>
       </c>
       <c r="N19" t="n">
-        <v>7.045283876208701</v>
+        <v>3.747942468653605</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="B20" t="n">
-        <v>3334</v>
+        <v>174</v>
       </c>
       <c r="C20" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
-        <v>60.07681334224453</v>
+        <v>62.72286771288932</v>
       </c>
       <c r="E20" t="n">
-        <v>482.105</v>
+        <v>506.77</v>
       </c>
       <c r="F20" t="n">
-        <v>152.7708531824745</v>
+        <v>145.3353437921283</v>
       </c>
       <c r="G20" t="n">
-        <v>85566.02214318189</v>
+        <v>95885.59006720989</v>
       </c>
       <c r="H20" t="n">
-        <v>-8341.358994065151</v>
+        <v>-7156.104970166496</v>
       </c>
       <c r="I20" t="n">
-        <v>5.205</v>
+        <v>7.42</v>
       </c>
       <c r="J20" t="n">
-        <v>19.23</v>
+        <v>27.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.505000000000001</v>
+        <v>3.815</v>
       </c>
       <c r="L20" t="n">
-        <v>3.41</v>
+        <v>5.319999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>221.2319672436798</v>
+        <v>236.408297083397</v>
       </c>
       <c r="N20" t="n">
-        <v>7.045283876208701</v>
+        <v>3.747942468653605</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="B21" t="n">
-        <v>3335</v>
+        <v>175</v>
       </c>
       <c r="C21" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="D21" t="n">
-        <v>60.70810056580181</v>
+        <v>63.75253334886362</v>
       </c>
       <c r="E21" t="n">
-        <v>483.735</v>
+        <v>510.695</v>
       </c>
       <c r="F21" t="n">
-        <v>152.2560744488963</v>
+        <v>144.2183537601443</v>
       </c>
       <c r="G21" t="n">
-        <v>82276.54722715581</v>
+        <v>93377.58940459072</v>
       </c>
       <c r="H21" t="n">
-        <v>-8277.649528251537</v>
+        <v>-6984.609218513938</v>
       </c>
       <c r="I21" t="n">
-        <v>5.175</v>
+        <v>7.555</v>
       </c>
       <c r="J21" t="n">
-        <v>19.92</v>
+        <v>28.91</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>3.395</v>
+        <v>5.53</v>
       </c>
       <c r="M21" t="n">
-        <v>217.5153677353537</v>
+        <v>236.4035709597147</v>
       </c>
       <c r="N21" t="n">
-        <v>7.120034056730911</v>
+        <v>3.687675725139311</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="B22" t="n">
-        <v>3336</v>
+        <v>176</v>
       </c>
       <c r="C22" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>60.70810056580181</v>
+        <v>62.68482890073624</v>
       </c>
       <c r="E22" t="n">
-        <v>483.735</v>
+        <v>506.78</v>
       </c>
       <c r="F22" t="n">
-        <v>152.2560744488963</v>
+        <v>145.3324759728814</v>
       </c>
       <c r="G22" t="n">
-        <v>85296.69238101688</v>
+        <v>95978.46077045727</v>
       </c>
       <c r="H22" t="n">
-        <v>-8277.649528251537</v>
+        <v>-7160.6990020513</v>
       </c>
       <c r="I22" t="n">
-        <v>5.175</v>
+        <v>7.485</v>
       </c>
       <c r="J22" t="n">
-        <v>19.92</v>
+        <v>27.32</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>3.82</v>
       </c>
       <c r="L22" t="n">
-        <v>3.395</v>
+        <v>5.350000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>217.5153677353537</v>
+        <v>240.0567372046249</v>
       </c>
       <c r="N22" t="n">
-        <v>7.120034056730911</v>
+        <v>3.687675725139311</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="B23" t="n">
-        <v>3337</v>
+        <v>177</v>
       </c>
       <c r="C23" t="n">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>58.71376252322056</v>
+        <v>63.72366610183674</v>
       </c>
       <c r="E23" t="n">
-        <v>479.23</v>
+        <v>510.535</v>
       </c>
       <c r="F23" t="n">
-        <v>153.6873571636518</v>
+        <v>144.2635513207456</v>
       </c>
       <c r="G23" t="n">
-        <v>81891.42168438996</v>
+        <v>93441.53343260537</v>
       </c>
       <c r="H23" t="n">
-        <v>-8480.898199442736</v>
+        <v>-6976.107853573215</v>
       </c>
       <c r="I23" t="n">
-        <v>5.175</v>
+        <v>7.44</v>
       </c>
       <c r="J23" t="n">
-        <v>18.18</v>
+        <v>28.795</v>
       </c>
       <c r="K23" t="n">
-        <v>2.435</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>3.33</v>
+        <v>5.485000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>225.333710165379</v>
+        <v>236.4030524625452</v>
       </c>
       <c r="N23" t="n">
-        <v>6.970276077183139</v>
+        <v>3.80186377787351</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>325</v>
+        <v>59</v>
       </c>
       <c r="B24" t="n">
-        <v>3338</v>
+        <v>181</v>
       </c>
       <c r="C24" t="n">
-        <v>325</v>
+        <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>58.71376252322056</v>
+        <v>40.9773557221506</v>
       </c>
       <c r="E24" t="n">
-        <v>479.23</v>
+        <v>458.23</v>
       </c>
       <c r="F24" t="n">
-        <v>153.6873571636518</v>
+        <v>160.7306203730372</v>
       </c>
       <c r="G24" t="n">
-        <v>85142.67575812041</v>
+        <v>73398.11852592908</v>
       </c>
       <c r="H24" t="n">
-        <v>-8480.898199442736</v>
+        <v>-9706.531263255853</v>
       </c>
       <c r="I24" t="n">
-        <v>5.175</v>
+        <v>4.850000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>18.18</v>
+        <v>12.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.435</v>
+        <v>1.94</v>
       </c>
       <c r="L24" t="n">
-        <v>3.33</v>
+        <v>2.72</v>
       </c>
       <c r="M24" t="n">
-        <v>225.333710165379</v>
+        <v>294.4779836189311</v>
       </c>
       <c r="N24" t="n">
-        <v>6.970276077183139</v>
+        <v>7.495265678103887</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>325</v>
+        <v>59</v>
       </c>
       <c r="B25" t="n">
-        <v>3339</v>
+        <v>182</v>
       </c>
       <c r="C25" t="n">
-        <v>325</v>
+        <v>59</v>
       </c>
       <c r="D25" t="n">
-        <v>59.37082968538485</v>
+        <v>38.52441116188371</v>
       </c>
       <c r="E25" t="n">
-        <v>480.64</v>
+        <v>455.745</v>
       </c>
       <c r="F25" t="n">
-        <v>153.2365016926117</v>
+        <v>161.607021851116</v>
       </c>
       <c r="G25" t="n">
-        <v>81850.6230975658</v>
+        <v>75452.17715328943</v>
       </c>
       <c r="H25" t="n">
-        <v>-8418.330910705699</v>
+        <v>-9878.972420826629</v>
       </c>
       <c r="I25" t="n">
-        <v>5.145</v>
+        <v>4.815</v>
       </c>
       <c r="J25" t="n">
-        <v>18.7</v>
+        <v>12.44</v>
       </c>
       <c r="K25" t="n">
-        <v>2.43</v>
+        <v>1.865</v>
       </c>
       <c r="L25" t="n">
-        <v>3.31</v>
+        <v>2.635</v>
       </c>
       <c r="M25" t="n">
-        <v>221.5131610596042</v>
+        <v>296.161896885483</v>
       </c>
       <c r="N25" t="n">
-        <v>7.045067755689094</v>
+        <v>7.495265678103887</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>325</v>
+        <v>59</v>
       </c>
       <c r="B26" t="n">
-        <v>3340</v>
+        <v>183</v>
       </c>
       <c r="C26" t="n">
-        <v>325</v>
+        <v>59</v>
       </c>
       <c r="D26" t="n">
-        <v>59.37082968538485</v>
+        <v>40.98635754933589</v>
       </c>
       <c r="E26" t="n">
-        <v>480.64</v>
+        <v>458.2</v>
       </c>
       <c r="F26" t="n">
-        <v>153.2365016926117</v>
+        <v>160.7411439841486</v>
       </c>
       <c r="G26" t="n">
-        <v>85024.20360029639</v>
+        <v>73418.30859712871</v>
       </c>
       <c r="H26" t="n">
-        <v>-8418.330910705699</v>
+        <v>-9696.657378852093</v>
       </c>
       <c r="I26" t="n">
-        <v>5.145</v>
+        <v>4.87</v>
       </c>
       <c r="J26" t="n">
-        <v>18.7</v>
+        <v>12.92</v>
       </c>
       <c r="K26" t="n">
-        <v>2.43</v>
+        <v>1.94</v>
       </c>
       <c r="L26" t="n">
-        <v>3.31</v>
+        <v>2.73</v>
       </c>
       <c r="M26" t="n">
-        <v>221.5131610596042</v>
+        <v>291.9657042891553</v>
       </c>
       <c r="N26" t="n">
-        <v>7.045067755689094</v>
+        <v>7.418540153204915</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>59</v>
+      </c>
+      <c r="B27" t="n">
+        <v>184</v>
+      </c>
+      <c r="C27" t="n">
+        <v>59</v>
+      </c>
+      <c r="D27" t="n">
+        <v>38.56032870014835</v>
+      </c>
+      <c r="E27" t="n">
+        <v>455.665</v>
+      </c>
+      <c r="F27" t="n">
+        <v>161.6353948043779</v>
+      </c>
+      <c r="G27" t="n">
+        <v>75469.52291616722</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-9867.807950792563</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="J27" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M27" t="n">
+        <v>293.6274949600626</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7.418540153204915</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>59</v>
+      </c>
+      <c r="B28" t="n">
+        <v>185</v>
+      </c>
+      <c r="C28" t="n">
+        <v>59</v>
+      </c>
+      <c r="D28" t="n">
+        <v>41.05832552566493</v>
+      </c>
+      <c r="E28" t="n">
+        <v>458.28</v>
+      </c>
+      <c r="F28" t="n">
+        <v>160.7130840829556</v>
+      </c>
+      <c r="G28" t="n">
+        <v>73402.49938786366</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-9715.007654016135</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="J28" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="M28" t="n">
+        <v>289.3654045982955</v>
+      </c>
+      <c r="N28" t="n">
+        <v>7.341903348620319</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>59</v>
+      </c>
+      <c r="B29" t="n">
+        <v>186</v>
+      </c>
+      <c r="C29" t="n">
+        <v>59</v>
+      </c>
+      <c r="D29" t="n">
+        <v>38.60067338071851</v>
+      </c>
+      <c r="E29" t="n">
+        <v>455.695</v>
+      </c>
+      <c r="F29" t="n">
+        <v>161.6247537794728</v>
+      </c>
+      <c r="G29" t="n">
+        <v>75516.87419687987</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-9854.414990533287</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.850000000000001</v>
+      </c>
+      <c r="J29" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="M29" t="n">
+        <v>289.883894364991</v>
+      </c>
+      <c r="N29" t="n">
+        <v>7.341903348620319</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>59</v>
+      </c>
+      <c r="B30" t="n">
+        <v>191</v>
+      </c>
+      <c r="C30" t="n">
+        <v>59</v>
+      </c>
+      <c r="D30" t="n">
+        <v>41.05326398960138</v>
+      </c>
+      <c r="E30" t="n">
+        <v>458.24</v>
+      </c>
+      <c r="F30" t="n">
+        <v>160.7271128088706</v>
+      </c>
+      <c r="G30" t="n">
+        <v>73402.17780345173</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-9708.728110519569</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="J30" t="n">
+        <v>12.935</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="M30" t="n">
+        <v>289.3642700751599</v>
+      </c>
+      <c r="N30" t="n">
+        <v>7.341637286398533</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>59</v>
+      </c>
+      <c r="B31" t="n">
+        <v>192</v>
+      </c>
+      <c r="C31" t="n">
+        <v>59</v>
+      </c>
+      <c r="D31" t="n">
+        <v>38.60928051066605</v>
+      </c>
+      <c r="E31" t="n">
+        <v>455.7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>161.6229804115358</v>
+      </c>
+      <c r="G31" t="n">
+        <v>75510.20549865822</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-9856.81851128905</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.845</v>
+      </c>
+      <c r="J31" t="n">
+        <v>12.475</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.865000000000001</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="M31" t="n">
+        <v>291.0050398087554</v>
+      </c>
+      <c r="N31" t="n">
+        <v>7.341637286398533</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>59</v>
+      </c>
+      <c r="B32" t="n">
+        <v>193</v>
+      </c>
+      <c r="C32" t="n">
+        <v>59</v>
+      </c>
+      <c r="D32" t="n">
+        <v>40.97130917359127</v>
+      </c>
+      <c r="E32" t="n">
+        <v>458.18</v>
+      </c>
+      <c r="F32" t="n">
+        <v>160.7481604904991</v>
+      </c>
+      <c r="G32" t="n">
+        <v>73395.18602689495</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-9703.848178238628</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="J32" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M32" t="n">
+        <v>294.4757410816344</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7.494583692457859</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>59</v>
+      </c>
+      <c r="B33" t="n">
+        <v>194</v>
+      </c>
+      <c r="C33" t="n">
+        <v>59</v>
+      </c>
+      <c r="D33" t="n">
+        <v>38.50683997894898</v>
+      </c>
+      <c r="E33" t="n">
+        <v>455.635</v>
+      </c>
+      <c r="F33" t="n">
+        <v>161.6460372305395</v>
+      </c>
+      <c r="G33" t="n">
+        <v>75456.82916942649</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-9864.325043403449</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2.629999999999999</v>
+      </c>
+      <c r="M33" t="n">
+        <v>296.1594479150303</v>
+      </c>
+      <c r="N33" t="n">
+        <v>7.494583692457859</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>59</v>
+      </c>
+      <c r="B34" t="n">
+        <v>195</v>
+      </c>
+      <c r="C34" t="n">
+        <v>59</v>
+      </c>
+      <c r="D34" t="n">
+        <v>40.99672358501572</v>
+      </c>
+      <c r="E34" t="n">
+        <v>458.16</v>
+      </c>
+      <c r="F34" t="n">
+        <v>160.7551776094309</v>
+      </c>
+      <c r="G34" t="n">
+        <v>73404.92308617364</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-9700.060513938573</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="J34" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="M34" t="n">
+        <v>291.9634769766074</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7.417979588623151</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>59</v>
+      </c>
+      <c r="B35" t="n">
+        <v>196</v>
+      </c>
+      <c r="C35" t="n">
+        <v>59</v>
+      </c>
+      <c r="D35" t="n">
+        <v>38.54921184530289</v>
+      </c>
+      <c r="E35" t="n">
+        <v>455.655</v>
+      </c>
+      <c r="F35" t="n">
+        <v>161.6389421240563</v>
+      </c>
+      <c r="G35" t="n">
+        <v>75472.80883105124</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-9864.516850801083</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.825</v>
+      </c>
+      <c r="J35" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M35" t="n">
+        <v>293.6250604742938</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7.417979588623151</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>59</v>
+      </c>
+      <c r="B36" t="n">
+        <v>197</v>
+      </c>
+      <c r="C36" t="n">
+        <v>59</v>
+      </c>
+      <c r="D36" t="n">
+        <v>41.02888586133871</v>
+      </c>
+      <c r="E36" t="n">
+        <v>458.27</v>
+      </c>
+      <c r="F36" t="n">
+        <v>160.7165910348416</v>
+      </c>
+      <c r="G36" t="n">
+        <v>73423.17398888041</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-9705.358885911242</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="J36" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L36" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="M36" t="n">
+        <v>289.3631850227439</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7.341428955296893</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>59</v>
+      </c>
+      <c r="B37" t="n">
+        <v>201</v>
+      </c>
+      <c r="C37" t="n">
+        <v>59</v>
+      </c>
+      <c r="D37" t="n">
+        <v>41.00138920966828</v>
+      </c>
+      <c r="E37" t="n">
+        <v>458.27</v>
+      </c>
+      <c r="F37" t="n">
+        <v>160.7165910348416</v>
+      </c>
+      <c r="G37" t="n">
+        <v>73404.85354808639</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-9710.831643342037</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="J37" t="n">
+        <v>12.905</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="M37" t="n">
+        <v>291.9624237548531</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7.417785548582478</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>59</v>
+      </c>
+      <c r="B38" t="n">
+        <v>202</v>
+      </c>
+      <c r="C38" t="n">
+        <v>59</v>
+      </c>
+      <c r="D38" t="n">
+        <v>38.53454198190661</v>
+      </c>
+      <c r="E38" t="n">
+        <v>455.67</v>
+      </c>
+      <c r="F38" t="n">
+        <v>161.6336212029251</v>
+      </c>
+      <c r="G38" t="n">
+        <v>75484.91531552121</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-9864.392172720651</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="J38" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M38" t="n">
+        <v>293.6239068446377</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7.417785548582478</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>59</v>
+      </c>
+      <c r="B39" t="n">
+        <v>203</v>
+      </c>
+      <c r="C39" t="n">
+        <v>59</v>
+      </c>
+      <c r="D39" t="n">
+        <v>41.03265988379305</v>
+      </c>
+      <c r="E39" t="n">
+        <v>458.22</v>
+      </c>
+      <c r="F39" t="n">
+        <v>160.7341280902992</v>
+      </c>
+      <c r="G39" t="n">
+        <v>73414.55355860955</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-9701.172159032079</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="J39" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="M39" t="n">
+        <v>289.3621360580096</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7.341258039070515</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>59</v>
+      </c>
+      <c r="B40" t="n">
+        <v>204</v>
+      </c>
+      <c r="C40" t="n">
+        <v>59</v>
+      </c>
+      <c r="D40" t="n">
+        <v>38.61922842769786</v>
+      </c>
+      <c r="E40" t="n">
+        <v>455.765</v>
+      </c>
+      <c r="F40" t="n">
+        <v>161.5999301691373</v>
+      </c>
+      <c r="G40" t="n">
+        <v>75502.10379334009</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-9870.726990868612</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="J40" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="M40" t="n">
+        <v>291.0027170557121</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7.341258039070515</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>59</v>
+      </c>
+      <c r="B41" t="n">
+        <v>205</v>
+      </c>
+      <c r="C41" t="n">
+        <v>59</v>
+      </c>
+      <c r="D41" t="n">
+        <v>40.98493884054005</v>
+      </c>
+      <c r="E41" t="n">
+        <v>458.18</v>
+      </c>
+      <c r="F41" t="n">
+        <v>160.7481604904991</v>
+      </c>
+      <c r="G41" t="n">
+        <v>73382.24830170402</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-9710.456702831312</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4.835</v>
+      </c>
+      <c r="J41" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="M41" t="n">
+        <v>294.4736484236201</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7.494175876509331</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>59</v>
+      </c>
+      <c r="B42" t="n">
+        <v>206</v>
+      </c>
+      <c r="C42" t="n">
+        <v>59</v>
+      </c>
+      <c r="D42" t="n">
+        <v>38.49329947954587</v>
+      </c>
+      <c r="E42" t="n">
+        <v>455.64</v>
+      </c>
+      <c r="F42" t="n">
+        <v>161.6442633955247</v>
+      </c>
+      <c r="G42" t="n">
+        <v>75467.02065436916</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-9866.13940993048</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4.795</v>
+      </c>
+      <c r="J42" t="n">
+        <v>12.425</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M42" t="n">
+        <v>296.1571802497453</v>
+      </c>
+      <c r="N42" t="n">
+        <v>7.494175876509331</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>61</v>
+      </c>
+      <c r="B43" t="n">
+        <v>211</v>
+      </c>
+      <c r="C43" t="n">
+        <v>61</v>
+      </c>
+      <c r="D43" t="n">
+        <v>74.12190309571783</v>
+      </c>
+      <c r="E43" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F43" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G43" t="n">
+        <v>66682.8737133993</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-6289.316725911981</v>
+      </c>
+      <c r="I43" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="J43" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.755000000000001</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6.445</v>
+      </c>
+      <c r="M43" t="n">
+        <v>207.217824678996</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3.372738683372571</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>61</v>
+      </c>
+      <c r="B44" t="n">
+        <v>212</v>
+      </c>
+      <c r="C44" t="n">
+        <v>61</v>
+      </c>
+      <c r="D44" t="n">
+        <v>74.12190309571783</v>
+      </c>
+      <c r="E44" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F44" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G44" t="n">
+        <v>66682.8737133993</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-6289.316725911981</v>
+      </c>
+      <c r="I44" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="J44" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4.755000000000001</v>
+      </c>
+      <c r="L44" t="n">
+        <v>6.445</v>
+      </c>
+      <c r="M44" t="n">
+        <v>207.217824678996</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3.372738683372571</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>61</v>
+      </c>
+      <c r="B45" t="n">
+        <v>213</v>
+      </c>
+      <c r="C45" t="n">
+        <v>61</v>
+      </c>
+      <c r="D45" t="n">
+        <v>74.13338422802028</v>
+      </c>
+      <c r="E45" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F45" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G45" t="n">
+        <v>66649.86800400796</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-6285.31530133066</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="J45" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L45" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="M45" t="n">
+        <v>206.8827056724729</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.47769334208065</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>61</v>
+      </c>
+      <c r="B46" t="n">
+        <v>214</v>
+      </c>
+      <c r="C46" t="n">
+        <v>61</v>
+      </c>
+      <c r="D46" t="n">
+        <v>74.13338422802028</v>
+      </c>
+      <c r="E46" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F46" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G46" t="n">
+        <v>66649.86800400796</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-6285.31530133066</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="J46" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L46" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="M46" t="n">
+        <v>206.8827056724729</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.47769334208065</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>61</v>
+      </c>
+      <c r="B47" t="n">
+        <v>215</v>
+      </c>
+      <c r="C47" t="n">
+        <v>61</v>
+      </c>
+      <c r="D47" t="n">
+        <v>74.14880961824358</v>
+      </c>
+      <c r="E47" t="n">
+        <v>526.345</v>
+      </c>
+      <c r="F47" t="n">
+        <v>139.9302590003455</v>
+      </c>
+      <c r="G47" t="n">
+        <v>66608.60561390752</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-6283.866645672346</v>
+      </c>
+      <c r="I47" t="n">
+        <v>7.985</v>
+      </c>
+      <c r="J47" t="n">
+        <v>49.245</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6.364999999999999</v>
+      </c>
+      <c r="M47" t="n">
+        <v>206.4256380380872</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.582641371625119</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>61</v>
+      </c>
+      <c r="B48" t="n">
+        <v>216</v>
+      </c>
+      <c r="C48" t="n">
+        <v>61</v>
+      </c>
+      <c r="D48" t="n">
+        <v>74.14880961824358</v>
+      </c>
+      <c r="E48" t="n">
+        <v>526.345</v>
+      </c>
+      <c r="F48" t="n">
+        <v>139.9302590003455</v>
+      </c>
+      <c r="G48" t="n">
+        <v>66608.60561390752</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-6283.866645672346</v>
+      </c>
+      <c r="I48" t="n">
+        <v>7.985</v>
+      </c>
+      <c r="J48" t="n">
+        <v>49.245</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L48" t="n">
+        <v>6.364999999999999</v>
+      </c>
+      <c r="M48" t="n">
+        <v>206.4256380380872</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.582641371625119</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>61</v>
+      </c>
+      <c r="B49" t="n">
+        <v>221</v>
+      </c>
+      <c r="C49" t="n">
+        <v>61</v>
+      </c>
+      <c r="D49" t="n">
+        <v>73.37679827130495</v>
+      </c>
+      <c r="E49" t="n">
+        <v>521.26</v>
+      </c>
+      <c r="F49" t="n">
+        <v>141.2953078569943</v>
+      </c>
+      <c r="G49" t="n">
+        <v>68781.31731616419</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-6492.116303984633</v>
+      </c>
+      <c r="I49" t="n">
+        <v>7.685</v>
+      </c>
+      <c r="J49" t="n">
+        <v>42.395</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L49" t="n">
+        <v>6.024999999999999</v>
+      </c>
+      <c r="M49" t="n">
+        <v>209.6950078301536</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3.768033513234366</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>61</v>
+      </c>
+      <c r="B50" t="n">
+        <v>222</v>
+      </c>
+      <c r="C50" t="n">
+        <v>61</v>
+      </c>
+      <c r="D50" t="n">
+        <v>73.37679827130495</v>
+      </c>
+      <c r="E50" t="n">
+        <v>521.26</v>
+      </c>
+      <c r="F50" t="n">
+        <v>141.2953078569943</v>
+      </c>
+      <c r="G50" t="n">
+        <v>68781.31731616419</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-6492.116303984633</v>
+      </c>
+      <c r="I50" t="n">
+        <v>7.685</v>
+      </c>
+      <c r="J50" t="n">
+        <v>42.395</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L50" t="n">
+        <v>6.024999999999999</v>
+      </c>
+      <c r="M50" t="n">
+        <v>209.6950078301536</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.768033513234366</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>61</v>
+      </c>
+      <c r="B51" t="n">
+        <v>223</v>
+      </c>
+      <c r="C51" t="n">
+        <v>61</v>
+      </c>
+      <c r="D51" t="n">
+        <v>72.55961484448041</v>
+      </c>
+      <c r="E51" t="n">
+        <v>516.375</v>
+      </c>
+      <c r="F51" t="n">
+        <v>142.6319867800278</v>
+      </c>
+      <c r="G51" t="n">
+        <v>71030.78308393959</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-6678.090032889222</v>
+      </c>
+      <c r="I51" t="n">
+        <v>7.615</v>
+      </c>
+      <c r="J51" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4.250000000000001</v>
+      </c>
+      <c r="L51" t="n">
+        <v>5.775000000000001</v>
+      </c>
+      <c r="M51" t="n">
+        <v>213.948400491082</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.722561737394678</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>61</v>
+      </c>
+      <c r="B52" t="n">
+        <v>224</v>
+      </c>
+      <c r="C52" t="n">
+        <v>61</v>
+      </c>
+      <c r="D52" t="n">
+        <v>72.55961484448041</v>
+      </c>
+      <c r="E52" t="n">
+        <v>516.375</v>
+      </c>
+      <c r="F52" t="n">
+        <v>142.6319867800278</v>
+      </c>
+      <c r="G52" t="n">
+        <v>71030.78308393959</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-6678.090032889222</v>
+      </c>
+      <c r="I52" t="n">
+        <v>7.615</v>
+      </c>
+      <c r="J52" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4.250000000000001</v>
+      </c>
+      <c r="L52" t="n">
+        <v>5.775000000000001</v>
+      </c>
+      <c r="M52" t="n">
+        <v>213.948400491082</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.722561737394678</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>61</v>
+      </c>
+      <c r="B53" t="n">
+        <v>225</v>
+      </c>
+      <c r="C53" t="n">
+        <v>61</v>
+      </c>
+      <c r="D53" t="n">
+        <v>72.57132895918926</v>
+      </c>
+      <c r="E53" t="n">
+        <v>516.33</v>
+      </c>
+      <c r="F53" t="n">
+        <v>142.6444176660989</v>
+      </c>
+      <c r="G53" t="n">
+        <v>70994.81539902162</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-6670.643209359158</v>
+      </c>
+      <c r="I53" t="n">
+        <v>7.505</v>
+      </c>
+      <c r="J53" t="n">
+        <v>37.655</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L53" t="n">
+        <v>5.735</v>
+      </c>
+      <c r="M53" t="n">
+        <v>213.440288276364</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.837988308955468</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>61</v>
+      </c>
+      <c r="B54" t="n">
+        <v>226</v>
+      </c>
+      <c r="C54" t="n">
+        <v>61</v>
+      </c>
+      <c r="D54" t="n">
+        <v>72.57132895918926</v>
+      </c>
+      <c r="E54" t="n">
+        <v>516.33</v>
+      </c>
+      <c r="F54" t="n">
+        <v>142.6444176660989</v>
+      </c>
+      <c r="G54" t="n">
+        <v>70994.81539902162</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-6670.643209359158</v>
+      </c>
+      <c r="I54" t="n">
+        <v>7.505</v>
+      </c>
+      <c r="J54" t="n">
+        <v>37.655</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L54" t="n">
+        <v>5.735</v>
+      </c>
+      <c r="M54" t="n">
+        <v>213.440288276364</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3.837988308955468</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>61</v>
+      </c>
+      <c r="B55" t="n">
+        <v>231</v>
+      </c>
+      <c r="C55" t="n">
+        <v>61</v>
+      </c>
+      <c r="D55" t="n">
+        <v>71.78371707622463</v>
+      </c>
+      <c r="E55" t="n">
+        <v>511.86</v>
+      </c>
+      <c r="F55" t="n">
+        <v>143.8901109161428</v>
+      </c>
+      <c r="G55" t="n">
+        <v>73134.07027755279</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-6839.538023837358</v>
+      </c>
+      <c r="I55" t="n">
+        <v>7.255</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.215</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L55" t="n">
+        <v>5.455</v>
+      </c>
+      <c r="M55" t="n">
+        <v>216.4965846822522</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4.018108455259386</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>61</v>
+      </c>
+      <c r="B56" t="n">
+        <v>232</v>
+      </c>
+      <c r="C56" t="n">
+        <v>61</v>
+      </c>
+      <c r="D56" t="n">
+        <v>71.78371707622463</v>
+      </c>
+      <c r="E56" t="n">
+        <v>511.86</v>
+      </c>
+      <c r="F56" t="n">
+        <v>143.8901109161428</v>
+      </c>
+      <c r="G56" t="n">
+        <v>73134.07027755279</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-6839.538023837358</v>
+      </c>
+      <c r="I56" t="n">
+        <v>7.255</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.215</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5.455</v>
+      </c>
+      <c r="M56" t="n">
+        <v>216.4965846822522</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4.018108455259386</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>61</v>
+      </c>
+      <c r="B57" t="n">
+        <v>233</v>
+      </c>
+      <c r="C57" t="n">
+        <v>61</v>
+      </c>
+      <c r="D57" t="n">
+        <v>71.80918880930597</v>
+      </c>
+      <c r="E57" t="n">
+        <v>512.0700000000001</v>
+      </c>
+      <c r="F57" t="n">
+        <v>143.8311015555234</v>
+      </c>
+      <c r="G57" t="n">
+        <v>73072.71219291775</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-6842.521640594845</v>
+      </c>
+      <c r="I57" t="n">
+        <v>7.165</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.265</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.040000000000001</v>
+      </c>
+      <c r="L57" t="n">
+        <v>5.425000000000001</v>
+      </c>
+      <c r="M57" t="n">
+        <v>215.7796287821913</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4.138760627105783</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>61</v>
+      </c>
+      <c r="B58" t="n">
+        <v>234</v>
+      </c>
+      <c r="C58" t="n">
+        <v>61</v>
+      </c>
+      <c r="D58" t="n">
+        <v>71.80918880930597</v>
+      </c>
+      <c r="E58" t="n">
+        <v>512.0700000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>143.8311015555234</v>
+      </c>
+      <c r="G58" t="n">
+        <v>73072.71219291775</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-6842.521640594845</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7.165</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.265</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4.040000000000001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>5.425000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>215.7796287821913</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4.138760627105783</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>61</v>
+      </c>
+      <c r="B59" t="n">
+        <v>235</v>
+      </c>
+      <c r="C59" t="n">
+        <v>61</v>
+      </c>
+      <c r="D59" t="n">
+        <v>70.9996745830536</v>
+      </c>
+      <c r="E59" t="n">
+        <v>507.73</v>
+      </c>
+      <c r="F59" t="n">
+        <v>145.0605482708071</v>
+      </c>
+      <c r="G59" t="n">
+        <v>75261.68866160722</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-7034.510920320518</v>
+      </c>
+      <c r="I59" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="J59" t="n">
+        <v>31.495</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.840000000000001</v>
+      </c>
+      <c r="L59" t="n">
+        <v>5.235</v>
+      </c>
+      <c r="M59" t="n">
+        <v>220.097016090333</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4.072315579270961</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>61</v>
+      </c>
+      <c r="B60" t="n">
+        <v>236</v>
+      </c>
+      <c r="C60" t="n">
+        <v>61</v>
+      </c>
+      <c r="D60" t="n">
+        <v>70.9996745830536</v>
+      </c>
+      <c r="E60" t="n">
+        <v>507.73</v>
+      </c>
+      <c r="F60" t="n">
+        <v>145.0605482708071</v>
+      </c>
+      <c r="G60" t="n">
+        <v>75261.68866160722</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-7034.510920320518</v>
+      </c>
+      <c r="I60" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="J60" t="n">
+        <v>31.495</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.840000000000001</v>
+      </c>
+      <c r="L60" t="n">
+        <v>5.235</v>
+      </c>
+      <c r="M60" t="n">
+        <v>220.097016090333</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4.072315579270961</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>62</v>
+      </c>
+      <c r="B61" t="n">
+        <v>241</v>
+      </c>
+      <c r="C61" t="n">
+        <v>62</v>
+      </c>
+      <c r="D61" t="n">
+        <v>74.12190309571783</v>
+      </c>
+      <c r="E61" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F61" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G61" t="n">
+        <v>66682.8737133993</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-6289.316725911981</v>
+      </c>
+      <c r="I61" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="J61" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4.755000000000001</v>
+      </c>
+      <c r="L61" t="n">
+        <v>6.445</v>
+      </c>
+      <c r="M61" t="n">
+        <v>207.217824678996</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3.372738683372571</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>62</v>
+      </c>
+      <c r="B62" t="n">
+        <v>242</v>
+      </c>
+      <c r="C62" t="n">
+        <v>62</v>
+      </c>
+      <c r="D62" t="n">
+        <v>74.12190309571783</v>
+      </c>
+      <c r="E62" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F62" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G62" t="n">
+        <v>66682.8737133993</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-6289.316725911981</v>
+      </c>
+      <c r="I62" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="J62" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4.755000000000001</v>
+      </c>
+      <c r="L62" t="n">
+        <v>6.445</v>
+      </c>
+      <c r="M62" t="n">
+        <v>207.217824678996</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3.372738683372571</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>243</v>
+      </c>
+      <c r="C63" t="n">
+        <v>62</v>
+      </c>
+      <c r="D63" t="n">
+        <v>74.13338422802028</v>
+      </c>
+      <c r="E63" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F63" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G63" t="n">
+        <v>66649.86800400796</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-6285.31530133066</v>
+      </c>
+      <c r="I63" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="J63" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L63" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="M63" t="n">
+        <v>206.8827056724729</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.47769334208065</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>244</v>
+      </c>
+      <c r="C64" t="n">
+        <v>62</v>
+      </c>
+      <c r="D64" t="n">
+        <v>74.13338422802028</v>
+      </c>
+      <c r="E64" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F64" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G64" t="n">
+        <v>66649.86800400796</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-6285.31530133066</v>
+      </c>
+      <c r="I64" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="J64" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L64" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="M64" t="n">
+        <v>206.8827056724729</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3.47769334208065</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" t="n">
+        <v>245</v>
+      </c>
+      <c r="C65" t="n">
+        <v>62</v>
+      </c>
+      <c r="D65" t="n">
+        <v>74.14880961824358</v>
+      </c>
+      <c r="E65" t="n">
+        <v>526.345</v>
+      </c>
+      <c r="F65" t="n">
+        <v>139.9302590003455</v>
+      </c>
+      <c r="G65" t="n">
+        <v>66608.60561390752</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-6283.866645672346</v>
+      </c>
+      <c r="I65" t="n">
+        <v>7.985</v>
+      </c>
+      <c r="J65" t="n">
+        <v>49.245</v>
+      </c>
+      <c r="K65" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L65" t="n">
+        <v>6.364999999999999</v>
+      </c>
+      <c r="M65" t="n">
+        <v>206.4256380380872</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3.582641371625119</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" t="n">
+        <v>246</v>
+      </c>
+      <c r="C66" t="n">
+        <v>62</v>
+      </c>
+      <c r="D66" t="n">
+        <v>74.14880961824358</v>
+      </c>
+      <c r="E66" t="n">
+        <v>526.345</v>
+      </c>
+      <c r="F66" t="n">
+        <v>139.9302590003455</v>
+      </c>
+      <c r="G66" t="n">
+        <v>66608.60561390752</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-6283.866645672346</v>
+      </c>
+      <c r="I66" t="n">
+        <v>7.985</v>
+      </c>
+      <c r="J66" t="n">
+        <v>49.245</v>
+      </c>
+      <c r="K66" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L66" t="n">
+        <v>6.364999999999999</v>
+      </c>
+      <c r="M66" t="n">
+        <v>206.4256380380872</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3.582641371625119</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" t="n">
+        <v>251</v>
+      </c>
+      <c r="C67" t="n">
+        <v>62</v>
+      </c>
+      <c r="D67" t="n">
+        <v>73.37679827130495</v>
+      </c>
+      <c r="E67" t="n">
+        <v>521.26</v>
+      </c>
+      <c r="F67" t="n">
+        <v>141.2953078569943</v>
+      </c>
+      <c r="G67" t="n">
+        <v>68781.31731616419</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-6492.116303984633</v>
+      </c>
+      <c r="I67" t="n">
+        <v>7.685</v>
+      </c>
+      <c r="J67" t="n">
+        <v>42.395</v>
+      </c>
+      <c r="K67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L67" t="n">
+        <v>6.024999999999999</v>
+      </c>
+      <c r="M67" t="n">
+        <v>209.6950078301536</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3.768033513234366</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>62</v>
+      </c>
+      <c r="B68" t="n">
+        <v>252</v>
+      </c>
+      <c r="C68" t="n">
+        <v>62</v>
+      </c>
+      <c r="D68" t="n">
+        <v>73.37679827130495</v>
+      </c>
+      <c r="E68" t="n">
+        <v>521.26</v>
+      </c>
+      <c r="F68" t="n">
+        <v>141.2953078569943</v>
+      </c>
+      <c r="G68" t="n">
+        <v>68781.31731616419</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-6492.116303984633</v>
+      </c>
+      <c r="I68" t="n">
+        <v>7.685</v>
+      </c>
+      <c r="J68" t="n">
+        <v>42.395</v>
+      </c>
+      <c r="K68" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L68" t="n">
+        <v>6.024999999999999</v>
+      </c>
+      <c r="M68" t="n">
+        <v>209.6950078301536</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3.768033513234366</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>62</v>
+      </c>
+      <c r="B69" t="n">
+        <v>253</v>
+      </c>
+      <c r="C69" t="n">
+        <v>62</v>
+      </c>
+      <c r="D69" t="n">
+        <v>72.55961484448041</v>
+      </c>
+      <c r="E69" t="n">
+        <v>516.375</v>
+      </c>
+      <c r="F69" t="n">
+        <v>142.6319867800278</v>
+      </c>
+      <c r="G69" t="n">
+        <v>71030.78308393959</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-6678.090032889222</v>
+      </c>
+      <c r="I69" t="n">
+        <v>7.615</v>
+      </c>
+      <c r="J69" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4.250000000000001</v>
+      </c>
+      <c r="L69" t="n">
+        <v>5.775000000000001</v>
+      </c>
+      <c r="M69" t="n">
+        <v>213.948400491082</v>
+      </c>
+      <c r="N69" t="n">
+        <v>3.722561737394678</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>62</v>
+      </c>
+      <c r="B70" t="n">
+        <v>254</v>
+      </c>
+      <c r="C70" t="n">
+        <v>62</v>
+      </c>
+      <c r="D70" t="n">
+        <v>72.55961484448041</v>
+      </c>
+      <c r="E70" t="n">
+        <v>516.375</v>
+      </c>
+      <c r="F70" t="n">
+        <v>142.6319867800278</v>
+      </c>
+      <c r="G70" t="n">
+        <v>71030.78308393959</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-6678.090032889222</v>
+      </c>
+      <c r="I70" t="n">
+        <v>7.615</v>
+      </c>
+      <c r="J70" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="K70" t="n">
+        <v>4.250000000000001</v>
+      </c>
+      <c r="L70" t="n">
+        <v>5.775000000000001</v>
+      </c>
+      <c r="M70" t="n">
+        <v>213.948400491082</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3.722561737394678</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>62</v>
+      </c>
+      <c r="B71" t="n">
+        <v>255</v>
+      </c>
+      <c r="C71" t="n">
+        <v>62</v>
+      </c>
+      <c r="D71" t="n">
+        <v>72.57132895918926</v>
+      </c>
+      <c r="E71" t="n">
+        <v>516.33</v>
+      </c>
+      <c r="F71" t="n">
+        <v>142.6444176660989</v>
+      </c>
+      <c r="G71" t="n">
+        <v>70994.81539902162</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-6670.643209359158</v>
+      </c>
+      <c r="I71" t="n">
+        <v>7.505</v>
+      </c>
+      <c r="J71" t="n">
+        <v>37.655</v>
+      </c>
+      <c r="K71" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L71" t="n">
+        <v>5.735</v>
+      </c>
+      <c r="M71" t="n">
+        <v>213.440288276364</v>
+      </c>
+      <c r="N71" t="n">
+        <v>3.837988308955468</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>62</v>
+      </c>
+      <c r="B72" t="n">
+        <v>256</v>
+      </c>
+      <c r="C72" t="n">
+        <v>62</v>
+      </c>
+      <c r="D72" t="n">
+        <v>72.57132895918926</v>
+      </c>
+      <c r="E72" t="n">
+        <v>516.33</v>
+      </c>
+      <c r="F72" t="n">
+        <v>142.6444176660989</v>
+      </c>
+      <c r="G72" t="n">
+        <v>70994.81539902162</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-6670.643209359158</v>
+      </c>
+      <c r="I72" t="n">
+        <v>7.505</v>
+      </c>
+      <c r="J72" t="n">
+        <v>37.655</v>
+      </c>
+      <c r="K72" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L72" t="n">
+        <v>5.735</v>
+      </c>
+      <c r="M72" t="n">
+        <v>213.440288276364</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.837988308955468</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>62</v>
+      </c>
+      <c r="B73" t="n">
+        <v>261</v>
+      </c>
+      <c r="C73" t="n">
+        <v>62</v>
+      </c>
+      <c r="D73" t="n">
+        <v>71.78371707622463</v>
+      </c>
+      <c r="E73" t="n">
+        <v>511.86</v>
+      </c>
+      <c r="F73" t="n">
+        <v>143.8901109161428</v>
+      </c>
+      <c r="G73" t="n">
+        <v>73134.07027755279</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-6839.538023837358</v>
+      </c>
+      <c r="I73" t="n">
+        <v>7.255</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.215</v>
+      </c>
+      <c r="K73" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L73" t="n">
+        <v>5.455</v>
+      </c>
+      <c r="M73" t="n">
+        <v>216.4965846822522</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4.018108455259386</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>62</v>
+      </c>
+      <c r="B74" t="n">
+        <v>262</v>
+      </c>
+      <c r="C74" t="n">
+        <v>62</v>
+      </c>
+      <c r="D74" t="n">
+        <v>71.78371707622463</v>
+      </c>
+      <c r="E74" t="n">
+        <v>511.86</v>
+      </c>
+      <c r="F74" t="n">
+        <v>143.8901109161428</v>
+      </c>
+      <c r="G74" t="n">
+        <v>73134.07027755279</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-6839.538023837358</v>
+      </c>
+      <c r="I74" t="n">
+        <v>7.255</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.215</v>
+      </c>
+      <c r="K74" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L74" t="n">
+        <v>5.455</v>
+      </c>
+      <c r="M74" t="n">
+        <v>216.4965846822522</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4.018108455259386</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>62</v>
+      </c>
+      <c r="B75" t="n">
+        <v>263</v>
+      </c>
+      <c r="C75" t="n">
+        <v>62</v>
+      </c>
+      <c r="D75" t="n">
+        <v>71.80918880930597</v>
+      </c>
+      <c r="E75" t="n">
+        <v>512.0700000000001</v>
+      </c>
+      <c r="F75" t="n">
+        <v>143.8311015555234</v>
+      </c>
+      <c r="G75" t="n">
+        <v>73072.71219291775</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-6842.521640594845</v>
+      </c>
+      <c r="I75" t="n">
+        <v>7.165</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.265</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4.040000000000001</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.425000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>215.7796287821913</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.138760627105783</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>62</v>
+      </c>
+      <c r="B76" t="n">
+        <v>264</v>
+      </c>
+      <c r="C76" t="n">
+        <v>62</v>
+      </c>
+      <c r="D76" t="n">
+        <v>71.80918880930597</v>
+      </c>
+      <c r="E76" t="n">
+        <v>512.0700000000001</v>
+      </c>
+      <c r="F76" t="n">
+        <v>143.8311015555234</v>
+      </c>
+      <c r="G76" t="n">
+        <v>73072.71219291775</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-6842.521640594845</v>
+      </c>
+      <c r="I76" t="n">
+        <v>7.165</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.265</v>
+      </c>
+      <c r="K76" t="n">
+        <v>4.040000000000001</v>
+      </c>
+      <c r="L76" t="n">
+        <v>5.425000000000001</v>
+      </c>
+      <c r="M76" t="n">
+        <v>215.7796287821913</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4.138760627105783</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>62</v>
+      </c>
+      <c r="B77" t="n">
+        <v>265</v>
+      </c>
+      <c r="C77" t="n">
+        <v>62</v>
+      </c>
+      <c r="D77" t="n">
+        <v>70.9996745830536</v>
+      </c>
+      <c r="E77" t="n">
+        <v>507.73</v>
+      </c>
+      <c r="F77" t="n">
+        <v>145.0605482708071</v>
+      </c>
+      <c r="G77" t="n">
+        <v>75261.68866160722</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-7034.510920320518</v>
+      </c>
+      <c r="I77" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="J77" t="n">
+        <v>31.495</v>
+      </c>
+      <c r="K77" t="n">
+        <v>3.840000000000001</v>
+      </c>
+      <c r="L77" t="n">
+        <v>5.235</v>
+      </c>
+      <c r="M77" t="n">
+        <v>220.097016090333</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4.072315579270961</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>62</v>
+      </c>
+      <c r="B78" t="n">
+        <v>266</v>
+      </c>
+      <c r="C78" t="n">
+        <v>62</v>
+      </c>
+      <c r="D78" t="n">
+        <v>70.9996745830536</v>
+      </c>
+      <c r="E78" t="n">
+        <v>507.73</v>
+      </c>
+      <c r="F78" t="n">
+        <v>145.0605482708071</v>
+      </c>
+      <c r="G78" t="n">
+        <v>75261.68866160722</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-7034.510920320518</v>
+      </c>
+      <c r="I78" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="J78" t="n">
+        <v>31.495</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3.840000000000001</v>
+      </c>
+      <c r="L78" t="n">
+        <v>5.235</v>
+      </c>
+      <c r="M78" t="n">
+        <v>220.097016090333</v>
+      </c>
+      <c r="N78" t="n">
+        <v>4.072315579270961</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>63</v>
+      </c>
+      <c r="B79" t="n">
+        <v>271</v>
+      </c>
+      <c r="C79" t="n">
+        <v>63</v>
+      </c>
+      <c r="D79" t="n">
+        <v>74.12190309571783</v>
+      </c>
+      <c r="E79" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F79" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G79" t="n">
+        <v>66682.8737133993</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-6289.316725911981</v>
+      </c>
+      <c r="I79" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="J79" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="K79" t="n">
+        <v>4.755000000000001</v>
+      </c>
+      <c r="L79" t="n">
+        <v>6.445</v>
+      </c>
+      <c r="M79" t="n">
+        <v>207.217824678996</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3.372738683372571</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>63</v>
+      </c>
+      <c r="B80" t="n">
+        <v>272</v>
+      </c>
+      <c r="C80" t="n">
+        <v>63</v>
+      </c>
+      <c r="D80" t="n">
+        <v>74.12190309571783</v>
+      </c>
+      <c r="E80" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F80" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G80" t="n">
+        <v>66682.8737133993</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-6289.316725911981</v>
+      </c>
+      <c r="I80" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="J80" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="K80" t="n">
+        <v>4.755000000000001</v>
+      </c>
+      <c r="L80" t="n">
+        <v>6.445</v>
+      </c>
+      <c r="M80" t="n">
+        <v>207.217824678996</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3.372738683372571</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>63</v>
+      </c>
+      <c r="B81" t="n">
+        <v>273</v>
+      </c>
+      <c r="C81" t="n">
+        <v>63</v>
+      </c>
+      <c r="D81" t="n">
+        <v>74.13338422802028</v>
+      </c>
+      <c r="E81" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F81" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G81" t="n">
+        <v>66649.86800400796</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-6285.31530133066</v>
+      </c>
+      <c r="I81" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="J81" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="K81" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L81" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="M81" t="n">
+        <v>206.8827056724729</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3.47769334208065</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>63</v>
+      </c>
+      <c r="B82" t="n">
+        <v>274</v>
+      </c>
+      <c r="C82" t="n">
+        <v>63</v>
+      </c>
+      <c r="D82" t="n">
+        <v>74.13338422802028</v>
+      </c>
+      <c r="E82" t="n">
+        <v>526.285</v>
+      </c>
+      <c r="F82" t="n">
+        <v>139.9462119831211</v>
+      </c>
+      <c r="G82" t="n">
+        <v>66649.86800400796</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-6285.31530133066</v>
+      </c>
+      <c r="I82" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="J82" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="K82" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L82" t="n">
+        <v>6.405</v>
+      </c>
+      <c r="M82" t="n">
+        <v>206.8827056724729</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3.47769334208065</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>63</v>
+      </c>
+      <c r="B83" t="n">
+        <v>275</v>
+      </c>
+      <c r="C83" t="n">
+        <v>63</v>
+      </c>
+      <c r="D83" t="n">
+        <v>74.14880961824358</v>
+      </c>
+      <c r="E83" t="n">
+        <v>526.345</v>
+      </c>
+      <c r="F83" t="n">
+        <v>139.9302590003455</v>
+      </c>
+      <c r="G83" t="n">
+        <v>66608.60561390752</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-6283.866645672346</v>
+      </c>
+      <c r="I83" t="n">
+        <v>7.985</v>
+      </c>
+      <c r="J83" t="n">
+        <v>49.245</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L83" t="n">
+        <v>6.364999999999999</v>
+      </c>
+      <c r="M83" t="n">
+        <v>206.4256380380872</v>
+      </c>
+      <c r="N83" t="n">
+        <v>3.582641371625119</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>63</v>
+      </c>
+      <c r="B84" t="n">
+        <v>276</v>
+      </c>
+      <c r="C84" t="n">
+        <v>63</v>
+      </c>
+      <c r="D84" t="n">
+        <v>74.14880961824358</v>
+      </c>
+      <c r="E84" t="n">
+        <v>526.345</v>
+      </c>
+      <c r="F84" t="n">
+        <v>139.9302590003455</v>
+      </c>
+      <c r="G84" t="n">
+        <v>66608.60561390752</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-6283.866645672346</v>
+      </c>
+      <c r="I84" t="n">
+        <v>7.985</v>
+      </c>
+      <c r="J84" t="n">
+        <v>49.245</v>
+      </c>
+      <c r="K84" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L84" t="n">
+        <v>6.364999999999999</v>
+      </c>
+      <c r="M84" t="n">
+        <v>206.4256380380872</v>
+      </c>
+      <c r="N84" t="n">
+        <v>3.582641371625119</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>63</v>
+      </c>
+      <c r="B85" t="n">
+        <v>281</v>
+      </c>
+      <c r="C85" t="n">
+        <v>63</v>
+      </c>
+      <c r="D85" t="n">
+        <v>73.37679827130495</v>
+      </c>
+      <c r="E85" t="n">
+        <v>521.26</v>
+      </c>
+      <c r="F85" t="n">
+        <v>141.2953078569943</v>
+      </c>
+      <c r="G85" t="n">
+        <v>68781.31731616419</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-6492.116303984633</v>
+      </c>
+      <c r="I85" t="n">
+        <v>7.685</v>
+      </c>
+      <c r="J85" t="n">
+        <v>42.395</v>
+      </c>
+      <c r="K85" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L85" t="n">
+        <v>6.024999999999999</v>
+      </c>
+      <c r="M85" t="n">
+        <v>209.6950078301536</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3.768033513234366</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>63</v>
+      </c>
+      <c r="B86" t="n">
+        <v>282</v>
+      </c>
+      <c r="C86" t="n">
+        <v>63</v>
+      </c>
+      <c r="D86" t="n">
+        <v>73.37679827130495</v>
+      </c>
+      <c r="E86" t="n">
+        <v>521.26</v>
+      </c>
+      <c r="F86" t="n">
+        <v>141.2953078569943</v>
+      </c>
+      <c r="G86" t="n">
+        <v>68781.31731616419</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-6492.116303984633</v>
+      </c>
+      <c r="I86" t="n">
+        <v>7.685</v>
+      </c>
+      <c r="J86" t="n">
+        <v>42.395</v>
+      </c>
+      <c r="K86" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L86" t="n">
+        <v>6.024999999999999</v>
+      </c>
+      <c r="M86" t="n">
+        <v>209.6950078301536</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3.768033513234366</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>63</v>
+      </c>
+      <c r="B87" t="n">
+        <v>283</v>
+      </c>
+      <c r="C87" t="n">
+        <v>63</v>
+      </c>
+      <c r="D87" t="n">
+        <v>72.55961484448041</v>
+      </c>
+      <c r="E87" t="n">
+        <v>516.375</v>
+      </c>
+      <c r="F87" t="n">
+        <v>142.6319867800278</v>
+      </c>
+      <c r="G87" t="n">
+        <v>71030.78308393959</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-6678.090032889222</v>
+      </c>
+      <c r="I87" t="n">
+        <v>7.615</v>
+      </c>
+      <c r="J87" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="K87" t="n">
+        <v>4.250000000000001</v>
+      </c>
+      <c r="L87" t="n">
+        <v>5.775000000000001</v>
+      </c>
+      <c r="M87" t="n">
+        <v>213.948400491082</v>
+      </c>
+      <c r="N87" t="n">
+        <v>3.722561737394678</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>63</v>
+      </c>
+      <c r="B88" t="n">
+        <v>284</v>
+      </c>
+      <c r="C88" t="n">
+        <v>63</v>
+      </c>
+      <c r="D88" t="n">
+        <v>72.55961484448041</v>
+      </c>
+      <c r="E88" t="n">
+        <v>516.375</v>
+      </c>
+      <c r="F88" t="n">
+        <v>142.6319867800278</v>
+      </c>
+      <c r="G88" t="n">
+        <v>71030.78308393959</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-6678.090032889222</v>
+      </c>
+      <c r="I88" t="n">
+        <v>7.615</v>
+      </c>
+      <c r="J88" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="K88" t="n">
+        <v>4.250000000000001</v>
+      </c>
+      <c r="L88" t="n">
+        <v>5.775000000000001</v>
+      </c>
+      <c r="M88" t="n">
+        <v>213.948400491082</v>
+      </c>
+      <c r="N88" t="n">
+        <v>3.722561737394678</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>63</v>
+      </c>
+      <c r="B89" t="n">
+        <v>285</v>
+      </c>
+      <c r="C89" t="n">
+        <v>63</v>
+      </c>
+      <c r="D89" t="n">
+        <v>72.57132895918926</v>
+      </c>
+      <c r="E89" t="n">
+        <v>516.33</v>
+      </c>
+      <c r="F89" t="n">
+        <v>142.6444176660989</v>
+      </c>
+      <c r="G89" t="n">
+        <v>70994.81539902162</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-6670.643209359158</v>
+      </c>
+      <c r="I89" t="n">
+        <v>7.505</v>
+      </c>
+      <c r="J89" t="n">
+        <v>37.655</v>
+      </c>
+      <c r="K89" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L89" t="n">
+        <v>5.735</v>
+      </c>
+      <c r="M89" t="n">
+        <v>213.440288276364</v>
+      </c>
+      <c r="N89" t="n">
+        <v>3.837988308955468</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>63</v>
+      </c>
+      <c r="B90" t="n">
+        <v>286</v>
+      </c>
+      <c r="C90" t="n">
+        <v>63</v>
+      </c>
+      <c r="D90" t="n">
+        <v>72.57132895918926</v>
+      </c>
+      <c r="E90" t="n">
+        <v>516.33</v>
+      </c>
+      <c r="F90" t="n">
+        <v>142.6444176660989</v>
+      </c>
+      <c r="G90" t="n">
+        <v>70994.81539902162</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-6670.643209359158</v>
+      </c>
+      <c r="I90" t="n">
+        <v>7.505</v>
+      </c>
+      <c r="J90" t="n">
+        <v>37.655</v>
+      </c>
+      <c r="K90" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L90" t="n">
+        <v>5.735</v>
+      </c>
+      <c r="M90" t="n">
+        <v>213.440288276364</v>
+      </c>
+      <c r="N90" t="n">
+        <v>3.837988308955468</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>63</v>
+      </c>
+      <c r="B91" t="n">
+        <v>291</v>
+      </c>
+      <c r="C91" t="n">
+        <v>63</v>
+      </c>
+      <c r="D91" t="n">
+        <v>71.78371707622463</v>
+      </c>
+      <c r="E91" t="n">
+        <v>511.86</v>
+      </c>
+      <c r="F91" t="n">
+        <v>143.8901109161428</v>
+      </c>
+      <c r="G91" t="n">
+        <v>73134.07027755279</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-6839.538023837358</v>
+      </c>
+      <c r="I91" t="n">
+        <v>7.255</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.215</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L91" t="n">
+        <v>5.455</v>
+      </c>
+      <c r="M91" t="n">
+        <v>216.4965846822522</v>
+      </c>
+      <c r="N91" t="n">
+        <v>4.018108455259386</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>63</v>
+      </c>
+      <c r="B92" t="n">
+        <v>292</v>
+      </c>
+      <c r="C92" t="n">
+        <v>63</v>
+      </c>
+      <c r="D92" t="n">
+        <v>71.78371707622463</v>
+      </c>
+      <c r="E92" t="n">
+        <v>511.86</v>
+      </c>
+      <c r="F92" t="n">
+        <v>143.8901109161428</v>
+      </c>
+      <c r="G92" t="n">
+        <v>73134.07027755279</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-6839.538023837358</v>
+      </c>
+      <c r="I92" t="n">
+        <v>7.255</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.215</v>
+      </c>
+      <c r="K92" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L92" t="n">
+        <v>5.455</v>
+      </c>
+      <c r="M92" t="n">
+        <v>216.4965846822522</v>
+      </c>
+      <c r="N92" t="n">
+        <v>4.018108455259386</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>63</v>
+      </c>
+      <c r="B93" t="n">
+        <v>293</v>
+      </c>
+      <c r="C93" t="n">
+        <v>63</v>
+      </c>
+      <c r="D93" t="n">
+        <v>71.80918880930597</v>
+      </c>
+      <c r="E93" t="n">
+        <v>512.0700000000001</v>
+      </c>
+      <c r="F93" t="n">
+        <v>143.8311015555234</v>
+      </c>
+      <c r="G93" t="n">
+        <v>73072.71219291775</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-6842.521640594845</v>
+      </c>
+      <c r="I93" t="n">
+        <v>7.165</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.265</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4.040000000000001</v>
+      </c>
+      <c r="L93" t="n">
+        <v>5.425000000000001</v>
+      </c>
+      <c r="M93" t="n">
+        <v>215.7796287821913</v>
+      </c>
+      <c r="N93" t="n">
+        <v>4.138760627105783</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>63</v>
+      </c>
+      <c r="B94" t="n">
+        <v>294</v>
+      </c>
+      <c r="C94" t="n">
+        <v>63</v>
+      </c>
+      <c r="D94" t="n">
+        <v>71.80918880930597</v>
+      </c>
+      <c r="E94" t="n">
+        <v>512.0700000000001</v>
+      </c>
+      <c r="F94" t="n">
+        <v>143.8311015555234</v>
+      </c>
+      <c r="G94" t="n">
+        <v>73072.71219291775</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-6842.521640594845</v>
+      </c>
+      <c r="I94" t="n">
+        <v>7.165</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.265</v>
+      </c>
+      <c r="K94" t="n">
+        <v>4.040000000000001</v>
+      </c>
+      <c r="L94" t="n">
+        <v>5.425000000000001</v>
+      </c>
+      <c r="M94" t="n">
+        <v>215.7796287821913</v>
+      </c>
+      <c r="N94" t="n">
+        <v>4.138760627105783</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>63</v>
+      </c>
+      <c r="B95" t="n">
+        <v>295</v>
+      </c>
+      <c r="C95" t="n">
+        <v>63</v>
+      </c>
+      <c r="D95" t="n">
+        <v>70.9996745830536</v>
+      </c>
+      <c r="E95" t="n">
+        <v>507.73</v>
+      </c>
+      <c r="F95" t="n">
+        <v>145.0605482708071</v>
+      </c>
+      <c r="G95" t="n">
+        <v>75261.68866160722</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-7034.510920320518</v>
+      </c>
+      <c r="I95" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="J95" t="n">
+        <v>31.495</v>
+      </c>
+      <c r="K95" t="n">
+        <v>3.840000000000001</v>
+      </c>
+      <c r="L95" t="n">
+        <v>5.235</v>
+      </c>
+      <c r="M95" t="n">
+        <v>220.097016090333</v>
+      </c>
+      <c r="N95" t="n">
+        <v>4.072315579270961</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>63</v>
+      </c>
+      <c r="B96" t="n">
+        <v>296</v>
+      </c>
+      <c r="C96" t="n">
+        <v>63</v>
+      </c>
+      <c r="D96" t="n">
+        <v>70.9996745830536</v>
+      </c>
+      <c r="E96" t="n">
+        <v>507.73</v>
+      </c>
+      <c r="F96" t="n">
+        <v>145.0605482708071</v>
+      </c>
+      <c r="G96" t="n">
+        <v>75261.68866160722</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-7034.510920320518</v>
+      </c>
+      <c r="I96" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="J96" t="n">
+        <v>31.495</v>
+      </c>
+      <c r="K96" t="n">
+        <v>3.840000000000001</v>
+      </c>
+      <c r="L96" t="n">
+        <v>5.235</v>
+      </c>
+      <c r="M96" t="n">
+        <v>220.097016090333</v>
+      </c>
+      <c r="N96" t="n">
+        <v>4.072315579270961</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>64</v>
+      </c>
+      <c r="B97" t="n">
+        <v>301</v>
+      </c>
+      <c r="C97" t="n">
+        <v>64</v>
+      </c>
+      <c r="D97" t="n">
+        <v>71.54869771804591</v>
+      </c>
+      <c r="E97" t="n">
+        <v>537.11</v>
+      </c>
+      <c r="F97" t="n">
+        <v>137.1257138640816</v>
+      </c>
+      <c r="G97" t="n">
+        <v>73303.49487072919</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-5951.816286348444</v>
+      </c>
+      <c r="I97" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="J97" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="K97" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="L97" t="n">
+        <v>7.654999999999999</v>
+      </c>
+      <c r="M97" t="n">
+        <v>206.1795438160647</v>
+      </c>
+      <c r="N97" t="n">
+        <v>2.614553482410988</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>64</v>
+      </c>
+      <c r="B98" t="n">
+        <v>311</v>
+      </c>
+      <c r="C98" t="n">
+        <v>64</v>
+      </c>
+      <c r="D98" t="n">
+        <v>70.66517949061581</v>
+      </c>
+      <c r="E98" t="n">
+        <v>531.3200000000001</v>
+      </c>
+      <c r="F98" t="n">
+        <v>138.6200259232418</v>
+      </c>
+      <c r="G98" t="n">
+        <v>75717.45520118967</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-6156.056276623038</v>
+      </c>
+      <c r="I98" t="n">
+        <v>9.005000000000001</v>
+      </c>
+      <c r="J98" t="n">
+        <v>49.635</v>
+      </c>
+      <c r="K98" t="n">
+        <v>5.119999999999999</v>
+      </c>
+      <c r="L98" t="n">
+        <v>7.074999999999999</v>
+      </c>
+      <c r="M98" t="n">
+        <v>209.3045894627159</v>
+      </c>
+      <c r="N98" t="n">
+        <v>2.923944181143443</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>64</v>
+      </c>
+      <c r="B99" t="n">
+        <v>312</v>
+      </c>
+      <c r="C99" t="n">
+        <v>64</v>
+      </c>
+      <c r="D99" t="n">
+        <v>70.66517949061581</v>
+      </c>
+      <c r="E99" t="n">
+        <v>531.3200000000001</v>
+      </c>
+      <c r="F99" t="n">
+        <v>138.6200259232418</v>
+      </c>
+      <c r="G99" t="n">
+        <v>75717.45520118967</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-6156.056276623038</v>
+      </c>
+      <c r="I99" t="n">
+        <v>9.005000000000001</v>
+      </c>
+      <c r="J99" t="n">
+        <v>49.635</v>
+      </c>
+      <c r="K99" t="n">
+        <v>5.119999999999999</v>
+      </c>
+      <c r="L99" t="n">
+        <v>7.074999999999999</v>
+      </c>
+      <c r="M99" t="n">
+        <v>209.3045894627159</v>
+      </c>
+      <c r="N99" t="n">
+        <v>2.923944181143443</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>64</v>
+      </c>
+      <c r="B100" t="n">
+        <v>313</v>
+      </c>
+      <c r="C100" t="n">
+        <v>64</v>
+      </c>
+      <c r="D100" t="n">
+        <v>69.77565710728355</v>
+      </c>
+      <c r="E100" t="n">
+        <v>526.4450000000001</v>
+      </c>
+      <c r="F100" t="n">
+        <v>139.9036787765804</v>
+      </c>
+      <c r="G100" t="n">
+        <v>78103.2093672008</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-6342.476222966495</v>
+      </c>
+      <c r="I100" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="J100" t="n">
+        <v>43.885</v>
+      </c>
+      <c r="K100" t="n">
+        <v>4.875000000000001</v>
+      </c>
+      <c r="L100" t="n">
+        <v>6.855000000000001</v>
+      </c>
+      <c r="M100" t="n">
+        <v>213.1469987176459</v>
+      </c>
+      <c r="N100" t="n">
+        <v>2.888353346779646</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>64</v>
+      </c>
+      <c r="B101" t="n">
+        <v>314</v>
+      </c>
+      <c r="C101" t="n">
+        <v>64</v>
+      </c>
+      <c r="D101" t="n">
+        <v>69.77565710728355</v>
+      </c>
+      <c r="E101" t="n">
+        <v>526.4450000000001</v>
+      </c>
+      <c r="F101" t="n">
+        <v>139.9036787765804</v>
+      </c>
+      <c r="G101" t="n">
+        <v>78103.2093672008</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-6342.476222966495</v>
+      </c>
+      <c r="I101" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="J101" t="n">
+        <v>43.885</v>
+      </c>
+      <c r="K101" t="n">
+        <v>4.875000000000001</v>
+      </c>
+      <c r="L101" t="n">
+        <v>6.855000000000001</v>
+      </c>
+      <c r="M101" t="n">
+        <v>213.1469987176459</v>
+      </c>
+      <c r="N101" t="n">
+        <v>2.888353346779646</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>64</v>
+      </c>
+      <c r="B102" t="n">
+        <v>321</v>
+      </c>
+      <c r="C102" t="n">
+        <v>64</v>
+      </c>
+      <c r="D102" t="n">
+        <v>68.90582944525694</v>
+      </c>
+      <c r="E102" t="n">
+        <v>521.5700000000001</v>
+      </c>
+      <c r="F102" t="n">
+        <v>141.2113276713324</v>
+      </c>
+      <c r="G102" t="n">
+        <v>80416.39970913071</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-6532.827246894246</v>
+      </c>
+      <c r="I102" t="n">
+        <v>8.505000000000001</v>
+      </c>
+      <c r="J102" t="n">
+        <v>39.715</v>
+      </c>
+      <c r="K102" t="n">
+        <v>4.615000000000001</v>
+      </c>
+      <c r="L102" t="n">
+        <v>6.440000000000001</v>
+      </c>
+      <c r="M102" t="n">
+        <v>216.1637526938089</v>
+      </c>
+      <c r="N102" t="n">
+        <v>3.119682589659338</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>64</v>
+      </c>
+      <c r="B103" t="n">
+        <v>322</v>
+      </c>
+      <c r="C103" t="n">
+        <v>64</v>
+      </c>
+      <c r="D103" t="n">
+        <v>68.90582944525694</v>
+      </c>
+      <c r="E103" t="n">
+        <v>521.5700000000001</v>
+      </c>
+      <c r="F103" t="n">
+        <v>141.2113276713324</v>
+      </c>
+      <c r="G103" t="n">
+        <v>80416.39970913071</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-6532.827246894246</v>
+      </c>
+      <c r="I103" t="n">
+        <v>8.505000000000001</v>
+      </c>
+      <c r="J103" t="n">
+        <v>39.715</v>
+      </c>
+      <c r="K103" t="n">
+        <v>4.615000000000001</v>
+      </c>
+      <c r="L103" t="n">
+        <v>6.440000000000001</v>
+      </c>
+      <c r="M103" t="n">
+        <v>216.1637526938089</v>
+      </c>
+      <c r="N103" t="n">
+        <v>3.119682589659338</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>64</v>
+      </c>
+      <c r="B104" t="n">
+        <v>323</v>
+      </c>
+      <c r="C104" t="n">
+        <v>64</v>
+      </c>
+      <c r="D104" t="n">
+        <v>68.92445708582909</v>
+      </c>
+      <c r="E104" t="n">
+        <v>521.495</v>
+      </c>
+      <c r="F104" t="n">
+        <v>141.2316363024322</v>
+      </c>
+      <c r="G104" t="n">
+        <v>80377.29334216085</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-6542.716469169233</v>
+      </c>
+      <c r="I104" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="J104" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="K104" t="n">
+        <v>4.605</v>
+      </c>
+      <c r="L104" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="M104" t="n">
+        <v>215.7470817212382</v>
+      </c>
+      <c r="N104" t="n">
+        <v>3.214122141179394</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>64</v>
+      </c>
+      <c r="B105" t="n">
+        <v>324</v>
+      </c>
+      <c r="C105" t="n">
+        <v>64</v>
+      </c>
+      <c r="D105" t="n">
+        <v>68.92445708582909</v>
+      </c>
+      <c r="E105" t="n">
+        <v>521.495</v>
+      </c>
+      <c r="F105" t="n">
+        <v>141.2316363024322</v>
+      </c>
+      <c r="G105" t="n">
+        <v>80377.29334216085</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-6542.716469169233</v>
+      </c>
+      <c r="I105" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="J105" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="K105" t="n">
+        <v>4.605</v>
+      </c>
+      <c r="L105" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="M105" t="n">
+        <v>215.7470817212382</v>
+      </c>
+      <c r="N105" t="n">
+        <v>3.214122141179394</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>65</v>
+      </c>
+      <c r="B106" t="n">
+        <v>341</v>
+      </c>
+      <c r="C106" t="n">
+        <v>65</v>
+      </c>
+      <c r="D106" t="n">
+        <v>63.96974025110715</v>
+      </c>
+      <c r="E106" t="n">
+        <v>510.675</v>
+      </c>
+      <c r="F106" t="n">
+        <v>144.2240019063727</v>
+      </c>
+      <c r="G106" t="n">
+        <v>92839.9261466462</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-6987.001290881008</v>
+      </c>
+      <c r="I106" t="n">
+        <v>8.055</v>
+      </c>
+      <c r="J106" t="n">
+        <v>29.325</v>
+      </c>
+      <c r="K106" t="n">
+        <v>4.025</v>
+      </c>
+      <c r="L106" t="n">
+        <v>5.745</v>
+      </c>
+      <c r="M106" t="n">
+        <v>232.4940552379874</v>
+      </c>
+      <c r="N106" t="n">
+        <v>3.295148869141022</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>65</v>
+      </c>
+      <c r="B107" t="n">
+        <v>342</v>
+      </c>
+      <c r="C107" t="n">
+        <v>65</v>
+      </c>
+      <c r="D107" t="n">
+        <v>63.00244765920053</v>
+      </c>
+      <c r="E107" t="n">
+        <v>507.02</v>
+      </c>
+      <c r="F107" t="n">
+        <v>145.2636822483075</v>
+      </c>
+      <c r="G107" t="n">
+        <v>95190.86002385501</v>
+      </c>
+      <c r="H107" t="n">
+        <v>-7139.955230845376</v>
+      </c>
+      <c r="I107" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="J107" t="n">
+        <v>28.205</v>
+      </c>
+      <c r="K107" t="n">
+        <v>3.890000000000001</v>
+      </c>
+      <c r="L107" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="M107" t="n">
+        <v>232.4941638653159</v>
+      </c>
+      <c r="N107" t="n">
+        <v>3.295148869141022</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>65</v>
+      </c>
+      <c r="B108" t="n">
+        <v>343</v>
+      </c>
+      <c r="C108" t="n">
+        <v>65</v>
+      </c>
+      <c r="D108" t="n">
+        <v>63.96593253758941</v>
+      </c>
+      <c r="E108" t="n">
+        <v>510.79</v>
+      </c>
+      <c r="F108" t="n">
+        <v>144.1915311058103</v>
+      </c>
+      <c r="G108" t="n">
+        <v>92846.28145636641</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-6982.099662381454</v>
+      </c>
+      <c r="I108" t="n">
+        <v>8.125</v>
+      </c>
+      <c r="J108" t="n">
+        <v>29.39</v>
+      </c>
+      <c r="K108" t="n">
+        <v>4.034999999999999</v>
+      </c>
+      <c r="L108" t="n">
+        <v>5.779999999999999</v>
+      </c>
+      <c r="M108" t="n">
+        <v>234.967436407216</v>
+      </c>
+      <c r="N108" t="n">
+        <v>3.255257973573699</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>65</v>
+      </c>
+      <c r="B109" t="n">
+        <v>344</v>
+      </c>
+      <c r="C109" t="n">
+        <v>65</v>
+      </c>
+      <c r="D109" t="n">
+        <v>62.95902475322752</v>
+      </c>
+      <c r="E109" t="n">
+        <v>507.115</v>
+      </c>
+      <c r="F109" t="n">
+        <v>145.236469387687</v>
+      </c>
+      <c r="G109" t="n">
+        <v>95316.71594807091</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-7174.263397335315</v>
+      </c>
+      <c r="I109" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J109" t="n">
+        <v>27.835</v>
+      </c>
+      <c r="K109" t="n">
+        <v>3.905</v>
+      </c>
+      <c r="L109" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="M109" t="n">
+        <v>238.1779438138752</v>
+      </c>
+      <c r="N109" t="n">
+        <v>3.255257973573699</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>65</v>
+      </c>
+      <c r="B110" t="n">
+        <v>345</v>
+      </c>
+      <c r="C110" t="n">
+        <v>65</v>
+      </c>
+      <c r="D110" t="n">
+        <v>63.93608606268292</v>
+      </c>
+      <c r="E110" t="n">
+        <v>510.55</v>
+      </c>
+      <c r="F110" t="n">
+        <v>144.2593128460227</v>
+      </c>
+      <c r="G110" t="n">
+        <v>92926.57339383452</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-6994.649337485628</v>
+      </c>
+      <c r="I110" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="J110" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="K110" t="n">
+        <v>4.004999999999999</v>
+      </c>
+      <c r="L110" t="n">
+        <v>5.694999999999999</v>
+      </c>
+      <c r="M110" t="n">
+        <v>234.9670309887708</v>
+      </c>
+      <c r="N110" t="n">
+        <v>3.356517838007766</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>65</v>
+      </c>
+      <c r="B111" t="n">
+        <v>346</v>
+      </c>
+      <c r="C111" t="n">
+        <v>65</v>
+      </c>
+      <c r="D111" t="n">
+        <v>62.92064310827005</v>
+      </c>
+      <c r="E111" t="n">
+        <v>506.82</v>
+      </c>
+      <c r="F111" t="n">
+        <v>145.3210058275855</v>
+      </c>
+      <c r="G111" t="n">
+        <v>95415.34466585703</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-7184.896760960375</v>
+      </c>
+      <c r="I111" t="n">
+        <v>7.925</v>
+      </c>
+      <c r="J111" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="K111" t="n">
+        <v>3.859999999999999</v>
+      </c>
+      <c r="L111" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="M111" t="n">
+        <v>236.9494456056658</v>
+      </c>
+      <c r="N111" t="n">
+        <v>3.356517838007766</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>65</v>
+      </c>
+      <c r="B112" t="n">
+        <v>347</v>
+      </c>
+      <c r="C112" t="n">
+        <v>65</v>
+      </c>
+      <c r="D112" t="n">
+        <v>63.89912560151584</v>
+      </c>
+      <c r="E112" t="n">
+        <v>510.315</v>
+      </c>
+      <c r="F112" t="n">
+        <v>144.3257442433338</v>
+      </c>
+      <c r="G112" t="n">
+        <v>93012.77236069505</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-6991.184758967391</v>
+      </c>
+      <c r="I112" t="n">
+        <v>7.815</v>
+      </c>
+      <c r="J112" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="K112" t="n">
+        <v>3.975000000000001</v>
+      </c>
+      <c r="L112" t="n">
+        <v>5.615000000000001</v>
+      </c>
+      <c r="M112" t="n">
+        <v>234.9666114635926</v>
+      </c>
+      <c r="N112" t="n">
+        <v>3.457772825936707</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>66</v>
+      </c>
+      <c r="B113" t="n">
+        <v>371</v>
+      </c>
+      <c r="C113" t="n">
+        <v>66</v>
+      </c>
+      <c r="D113" t="n">
+        <v>45.85094928070421</v>
+      </c>
+      <c r="E113" t="n">
+        <v>463.65</v>
+      </c>
+      <c r="F113" t="n">
+        <v>158.8517031673393</v>
+      </c>
+      <c r="G113" t="n">
+        <v>75858.00828133599</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-9384.691289700286</v>
+      </c>
+      <c r="I113" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J113" t="n">
+        <v>14.535</v>
+      </c>
+      <c r="K113" t="n">
+        <v>2.130000000000001</v>
+      </c>
+      <c r="L113" t="n">
+        <v>3.055000000000001</v>
+      </c>
+      <c r="M113" t="n">
+        <v>268.6684422379022</v>
+      </c>
+      <c r="N113" t="n">
+        <v>6.066795777615476</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>71</v>
+      </c>
+      <c r="B114" t="n">
+        <v>521</v>
+      </c>
+      <c r="C114" t="n">
+        <v>71</v>
+      </c>
+      <c r="D114" t="n">
+        <v>70.63725829151778</v>
+      </c>
+      <c r="E114" t="n">
+        <v>515.085</v>
+      </c>
+      <c r="F114" t="n">
+        <v>142.9892001777121</v>
+      </c>
+      <c r="G114" t="n">
+        <v>76077.86276139031</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-6768.259454829606</v>
+      </c>
+      <c r="I114" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.675</v>
+      </c>
+      <c r="K114" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="L114" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M114" t="n">
+        <v>220.2550194758885</v>
+      </c>
+      <c r="N114" t="n">
+        <v>3.409914546557408</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>71</v>
+      </c>
+      <c r="B115" t="n">
+        <v>522</v>
+      </c>
+      <c r="C115" t="n">
+        <v>71</v>
+      </c>
+      <c r="D115" t="n">
+        <v>70.63725829151778</v>
+      </c>
+      <c r="E115" t="n">
+        <v>515.085</v>
+      </c>
+      <c r="F115" t="n">
+        <v>142.9892001777121</v>
+      </c>
+      <c r="G115" t="n">
+        <v>76077.86276139031</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-6768.259454829606</v>
+      </c>
+      <c r="I115" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.675</v>
+      </c>
+      <c r="K115" t="n">
+        <v>4.285</v>
+      </c>
+      <c r="L115" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="M115" t="n">
+        <v>220.2550194758885</v>
+      </c>
+      <c r="N115" t="n">
+        <v>3.409914546557408</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>71</v>
+      </c>
+      <c r="B116" t="n">
+        <v>523</v>
+      </c>
+      <c r="C116" t="n">
+        <v>71</v>
+      </c>
+      <c r="D116" t="n">
+        <v>69.7091506616992</v>
+      </c>
+      <c r="E116" t="n">
+        <v>510.56</v>
+      </c>
+      <c r="F116" t="n">
+        <v>144.2564873345677</v>
+      </c>
+      <c r="G116" t="n">
+        <v>78542.90045918446</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-6964.449900193348</v>
+      </c>
+      <c r="I116" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="J116" t="n">
+        <v>32.055</v>
+      </c>
+      <c r="K116" t="n">
+        <v>4.090000000000001</v>
+      </c>
+      <c r="L116" t="n">
+        <v>5.775</v>
+      </c>
+      <c r="M116" t="n">
+        <v>225.1725259077926</v>
+      </c>
+      <c r="N116" t="n">
+        <v>3.368658319417166</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>71</v>
+      </c>
+      <c r="B117" t="n">
+        <v>531</v>
+      </c>
+      <c r="C117" t="n">
+        <v>71</v>
+      </c>
+      <c r="D117" t="n">
+        <v>68.82266937836316</v>
+      </c>
+      <c r="E117" t="n">
+        <v>506.13</v>
+      </c>
+      <c r="F117" t="n">
+        <v>145.5191199366504</v>
+      </c>
+      <c r="G117" t="n">
+        <v>80857.84632721412</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-7134.266405967172</v>
+      </c>
+      <c r="I117" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="J117" t="n">
+        <v>29.765</v>
+      </c>
+      <c r="K117" t="n">
+        <v>3.875000000000001</v>
+      </c>
+      <c r="L117" t="n">
+        <v>5.435</v>
+      </c>
+      <c r="M117" t="n">
+        <v>227.3741297647134</v>
+      </c>
+      <c r="N117" t="n">
+        <v>3.63680797651955</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>71</v>
+      </c>
+      <c r="B118" t="n">
+        <v>532</v>
+      </c>
+      <c r="C118" t="n">
+        <v>71</v>
+      </c>
+      <c r="D118" t="n">
+        <v>68.82266937836316</v>
+      </c>
+      <c r="E118" t="n">
+        <v>506.13</v>
+      </c>
+      <c r="F118" t="n">
+        <v>145.5191199366504</v>
+      </c>
+      <c r="G118" t="n">
+        <v>80857.84632721412</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-7134.266405967172</v>
+      </c>
+      <c r="I118" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="J118" t="n">
+        <v>29.765</v>
+      </c>
+      <c r="K118" t="n">
+        <v>3.875000000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>5.435</v>
+      </c>
+      <c r="M118" t="n">
+        <v>227.3741297647134</v>
+      </c>
+      <c r="N118" t="n">
+        <v>3.63680797651955</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>71</v>
+      </c>
+      <c r="B119" t="n">
+        <v>533</v>
+      </c>
+      <c r="C119" t="n">
+        <v>71</v>
+      </c>
+      <c r="D119" t="n">
+        <v>68.85741088154208</v>
+      </c>
+      <c r="E119" t="n">
+        <v>506.125</v>
+      </c>
+      <c r="F119" t="n">
+        <v>145.5205575174845</v>
+      </c>
+      <c r="G119" t="n">
+        <v>80771.43517742303</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-7133.57772944515</v>
+      </c>
+      <c r="I119" t="n">
+        <v>7.435</v>
+      </c>
+      <c r="J119" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="K119" t="n">
+        <v>3.860000000000001</v>
+      </c>
+      <c r="L119" t="n">
+        <v>5.375000000000001</v>
+      </c>
+      <c r="M119" t="n">
+        <v>226.3071835690666</v>
+      </c>
+      <c r="N119" t="n">
+        <v>3.74627879679292</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>71</v>
+      </c>
+      <c r="B120" t="n">
+        <v>534</v>
+      </c>
+      <c r="C120" t="n">
+        <v>71</v>
+      </c>
+      <c r="D120" t="n">
+        <v>68.85741088154208</v>
+      </c>
+      <c r="E120" t="n">
+        <v>506.125</v>
+      </c>
+      <c r="F120" t="n">
+        <v>145.5205575174845</v>
+      </c>
+      <c r="G120" t="n">
+        <v>80771.43517742303</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-7133.57772944515</v>
+      </c>
+      <c r="I120" t="n">
+        <v>7.435</v>
+      </c>
+      <c r="J120" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="K120" t="n">
+        <v>3.860000000000001</v>
+      </c>
+      <c r="L120" t="n">
+        <v>5.375000000000001</v>
+      </c>
+      <c r="M120" t="n">
+        <v>226.3071835690666</v>
+      </c>
+      <c r="N120" t="n">
+        <v>3.74627879679292</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>71</v>
+      </c>
+      <c r="B121" t="n">
+        <v>535</v>
+      </c>
+      <c r="C121" t="n">
+        <v>71</v>
+      </c>
+      <c r="D121" t="n">
+        <v>67.92635023231183</v>
+      </c>
+      <c r="E121" t="n">
+        <v>502.31</v>
+      </c>
+      <c r="F121" t="n">
+        <v>146.6257732745454</v>
+      </c>
+      <c r="G121" t="n">
+        <v>83184.53339391849</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-7328.797861546023</v>
+      </c>
+      <c r="I121" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="J121" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="K121" t="n">
+        <v>3.705</v>
+      </c>
+      <c r="L121" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="M121" t="n">
+        <v>231.3213487402756</v>
+      </c>
+      <c r="N121" t="n">
+        <v>3.685991325566078</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>72</v>
+      </c>
+      <c r="B122" t="n">
+        <v>541</v>
+      </c>
+      <c r="C122" t="n">
+        <v>72</v>
+      </c>
+      <c r="D122" t="n">
+        <v>73.63680569874325</v>
+      </c>
+      <c r="E122" t="n">
+        <v>531.9400000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>138.4584580470295</v>
+      </c>
+      <c r="G122" t="n">
+        <v>67861.37583128129</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-6091.66480902716</v>
+      </c>
+      <c r="I122" t="n">
+        <v>8.775</v>
+      </c>
+      <c r="J122" t="n">
+        <v>49.635</v>
+      </c>
+      <c r="K122" t="n">
+        <v>5.185</v>
+      </c>
+      <c r="L122" t="n">
+        <v>7.035000000000001</v>
+      </c>
+      <c r="M122" t="n">
+        <v>209.6110833090756</v>
+      </c>
+      <c r="N122" t="n">
+        <v>3.084218089377052</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>72</v>
+      </c>
+      <c r="B123" t="n">
+        <v>542</v>
+      </c>
+      <c r="C123" t="n">
+        <v>72</v>
+      </c>
+      <c r="D123" t="n">
+        <v>73.63680569874325</v>
+      </c>
+      <c r="E123" t="n">
+        <v>531.9400000000001</v>
+      </c>
+      <c r="F123" t="n">
+        <v>138.4584580470295</v>
+      </c>
+      <c r="G123" t="n">
+        <v>67861.37583128129</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-6091.66480902716</v>
+      </c>
+      <c r="I123" t="n">
+        <v>8.775</v>
+      </c>
+      <c r="J123" t="n">
+        <v>49.635</v>
+      </c>
+      <c r="K123" t="n">
+        <v>5.185</v>
+      </c>
+      <c r="L123" t="n">
+        <v>7.035000000000001</v>
+      </c>
+      <c r="M123" t="n">
+        <v>209.6110833090756</v>
+      </c>
+      <c r="N123" t="n">
+        <v>3.084218089377052</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>72</v>
+      </c>
+      <c r="B124" t="n">
+        <v>543</v>
+      </c>
+      <c r="C124" t="n">
+        <v>72</v>
+      </c>
+      <c r="D124" t="n">
+        <v>73.65048400285794</v>
+      </c>
+      <c r="E124" t="n">
+        <v>531.925</v>
+      </c>
+      <c r="F124" t="n">
+        <v>138.4623625013618</v>
+      </c>
+      <c r="G124" t="n">
+        <v>67824.46830032681</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-6090.527488757602</v>
+      </c>
+      <c r="I124" t="n">
+        <v>8.645</v>
+      </c>
+      <c r="J124" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="K124" t="n">
+        <v>5.190000000000001</v>
+      </c>
+      <c r="L124" t="n">
+        <v>6.985000000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>209.2135502794069</v>
+      </c>
+      <c r="N124" t="n">
+        <v>3.180434190643461</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>72</v>
+      </c>
+      <c r="B125" t="n">
+        <v>544</v>
+      </c>
+      <c r="C125" t="n">
+        <v>72</v>
+      </c>
+      <c r="D125" t="n">
+        <v>73.65048400285794</v>
+      </c>
+      <c r="E125" t="n">
+        <v>531.925</v>
+      </c>
+      <c r="F125" t="n">
+        <v>138.4623625013618</v>
+      </c>
+      <c r="G125" t="n">
+        <v>67824.46830032681</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-6090.527488757602</v>
+      </c>
+      <c r="I125" t="n">
+        <v>8.645</v>
+      </c>
+      <c r="J125" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="K125" t="n">
+        <v>5.190000000000001</v>
+      </c>
+      <c r="L125" t="n">
+        <v>6.985000000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>209.2135502794069</v>
+      </c>
+      <c r="N125" t="n">
+        <v>3.180434190643461</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>72</v>
+      </c>
+      <c r="B126" t="n">
+        <v>551</v>
+      </c>
+      <c r="C126" t="n">
+        <v>72</v>
+      </c>
+      <c r="D126" t="n">
+        <v>72.870672319619</v>
+      </c>
+      <c r="E126" t="n">
+        <v>526.675</v>
+      </c>
+      <c r="F126" t="n">
+        <v>139.842582567118</v>
+      </c>
+      <c r="G126" t="n">
+        <v>70001.32184471084</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-6284.006732179307</v>
+      </c>
+      <c r="I126" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="K126" t="n">
+        <v>4.905</v>
+      </c>
+      <c r="L126" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="M126" t="n">
+        <v>211.9816059853208</v>
+      </c>
+      <c r="N126" t="n">
+        <v>3.446605420471301</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>72</v>
+      </c>
+      <c r="B127" t="n">
+        <v>552</v>
+      </c>
+      <c r="C127" t="n">
+        <v>72</v>
+      </c>
+      <c r="D127" t="n">
+        <v>72.870672319619</v>
+      </c>
+      <c r="E127" t="n">
+        <v>526.675</v>
+      </c>
+      <c r="F127" t="n">
+        <v>139.842582567118</v>
+      </c>
+      <c r="G127" t="n">
+        <v>70001.32184471084</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-6284.006732179307</v>
+      </c>
+      <c r="I127" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J127" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="K127" t="n">
+        <v>4.905</v>
+      </c>
+      <c r="L127" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="M127" t="n">
+        <v>211.9816059853208</v>
+      </c>
+      <c r="N127" t="n">
+        <v>3.446605420471301</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>73</v>
+      </c>
+      <c r="B128" t="n">
+        <v>571</v>
+      </c>
+      <c r="C128" t="n">
+        <v>73</v>
+      </c>
+      <c r="D128" t="n">
+        <v>65.0189256113774</v>
+      </c>
+      <c r="E128" t="n">
+        <v>500.13</v>
+      </c>
+      <c r="F128" t="n">
+        <v>147.2648954742504</v>
+      </c>
+      <c r="G128" t="n">
+        <v>90414.58819770042</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-7453.20691603694</v>
+      </c>
+      <c r="I128" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="J128" t="n">
+        <v>24.645</v>
+      </c>
+      <c r="K128" t="n">
+        <v>3.510000000000001</v>
+      </c>
+      <c r="L128" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="M128" t="n">
+        <v>242.5036999166232</v>
+      </c>
+      <c r="N128" t="n">
+        <v>4.325652886299918</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>73</v>
+      </c>
+      <c r="B129" t="n">
+        <v>572</v>
+      </c>
+      <c r="C129" t="n">
+        <v>73</v>
+      </c>
+      <c r="D129" t="n">
+        <v>64.01005379895568</v>
+      </c>
+      <c r="E129" t="n">
+        <v>496.53</v>
+      </c>
+      <c r="F129" t="n">
+        <v>148.3326126790664</v>
+      </c>
+      <c r="G129" t="n">
+        <v>92870.42060588002</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-7599.857474754852</v>
+      </c>
+      <c r="I129" t="n">
+        <v>6.685</v>
+      </c>
+      <c r="J129" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="K129" t="n">
+        <v>3.350000000000001</v>
+      </c>
+      <c r="L129" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="M129" t="n">
+        <v>242.5038530412947</v>
+      </c>
+      <c r="N129" t="n">
+        <v>4.325652886299918</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>73</v>
+      </c>
+      <c r="B130" t="n">
+        <v>573</v>
+      </c>
+      <c r="C130" t="n">
+        <v>73</v>
+      </c>
+      <c r="D130" t="n">
+        <v>65.00586423147543</v>
+      </c>
+      <c r="E130" t="n">
+        <v>499.995</v>
+      </c>
+      <c r="F130" t="n">
+        <v>147.3046573936477</v>
+      </c>
+      <c r="G130" t="n">
+        <v>90430.39392653653</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-7431.584094181566</v>
+      </c>
+      <c r="I130" t="n">
+        <v>6.745</v>
+      </c>
+      <c r="J130" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="K130" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="L130" t="n">
+        <v>4.819999999999999</v>
+      </c>
+      <c r="M130" t="n">
+        <v>241.1170822408315</v>
+      </c>
+      <c r="N130" t="n">
+        <v>4.325794468912928</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>73</v>
+      </c>
+      <c r="B131" t="n">
+        <v>574</v>
+      </c>
+      <c r="C131" t="n">
+        <v>73</v>
+      </c>
+      <c r="D131" t="n">
+        <v>64.03134293538385</v>
+      </c>
+      <c r="E131" t="n">
+        <v>496.7</v>
+      </c>
+      <c r="F131" t="n">
+        <v>148.2818445209118</v>
+      </c>
+      <c r="G131" t="n">
+        <v>92832.95149401789</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-7615.960870664787</v>
+      </c>
+      <c r="I131" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="J131" t="n">
+        <v>23.865</v>
+      </c>
+      <c r="K131" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L131" t="n">
+        <v>4.659999999999999</v>
+      </c>
+      <c r="M131" t="n">
+        <v>241.1171672413651</v>
+      </c>
+      <c r="N131" t="n">
+        <v>4.325794468912928</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>73</v>
+      </c>
+      <c r="B132" t="n">
+        <v>575</v>
+      </c>
+      <c r="C132" t="n">
+        <v>73</v>
+      </c>
+      <c r="D132" t="n">
+        <v>65.02271771627692</v>
+      </c>
+      <c r="E132" t="n">
+        <v>500.055</v>
+      </c>
+      <c r="F132" t="n">
+        <v>147.2869827789681</v>
+      </c>
+      <c r="G132" t="n">
+        <v>90397.35293280808</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-7441.895970371301</v>
+      </c>
+      <c r="I132" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="J132" t="n">
+        <v>24.635</v>
+      </c>
+      <c r="K132" t="n">
+        <v>3.510000000000001</v>
+      </c>
+      <c r="L132" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="M132" t="n">
+        <v>239.6086989503265</v>
+      </c>
+      <c r="N132" t="n">
+        <v>4.325900322838593</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>322</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3241</v>
+      </c>
+      <c r="C133" t="n">
+        <v>322</v>
+      </c>
+      <c r="D133" t="n">
+        <v>47.71297461825204</v>
+      </c>
+      <c r="E133" t="n">
+        <v>455.72</v>
+      </c>
+      <c r="F133" t="n">
+        <v>161.6158873289232</v>
+      </c>
+      <c r="G133" t="n">
+        <v>72985.52634566055</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-9934.238467891963</v>
+      </c>
+      <c r="I133" t="n">
+        <v>4.555</v>
+      </c>
+      <c r="J133" t="n">
+        <v>11.485</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L133" t="n">
+        <v>2.355</v>
+      </c>
+      <c r="M133" t="n">
+        <v>247.1737965943455</v>
+      </c>
+      <c r="N133" t="n">
+        <v>7.913161707222892</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>322</v>
+      </c>
+      <c r="B134" t="n">
+        <v>3242</v>
+      </c>
+      <c r="C134" t="n">
+        <v>322</v>
+      </c>
+      <c r="D134" t="n">
+        <v>46.08227668192797</v>
+      </c>
+      <c r="E134" t="n">
+        <v>453.91</v>
+      </c>
+      <c r="F134" t="n">
+        <v>162.2603427409329</v>
+      </c>
+      <c r="G134" t="n">
+        <v>75372.98344159761</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-10061.31337515757</v>
+      </c>
+      <c r="I134" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="J134" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="L134" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M134" t="n">
+        <v>247.1737969472284</v>
+      </c>
+      <c r="N134" t="n">
+        <v>7.936311392178908</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>322</v>
+      </c>
+      <c r="B135" t="n">
+        <v>3243</v>
+      </c>
+      <c r="C135" t="n">
+        <v>322</v>
+      </c>
+      <c r="D135" t="n">
+        <v>48.4242120173468</v>
+      </c>
+      <c r="E135" t="n">
+        <v>456.89</v>
+      </c>
+      <c r="F135" t="n">
+        <v>161.2020227484446</v>
+      </c>
+      <c r="G135" t="n">
+        <v>73443.31079410459</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-9864.135528675084</v>
+      </c>
+      <c r="I135" t="n">
+        <v>4.575</v>
+      </c>
+      <c r="J135" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1.649999999999999</v>
+      </c>
+      <c r="L135" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M135" t="n">
+        <v>242.6084328998986</v>
+      </c>
+      <c r="N135" t="n">
+        <v>7.846769612610431</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>322</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3244</v>
+      </c>
+      <c r="C136" t="n">
+        <v>322</v>
+      </c>
+      <c r="D136" t="n">
+        <v>46.88798101033034</v>
+      </c>
+      <c r="E136" t="n">
+        <v>455.065</v>
+      </c>
+      <c r="F136" t="n">
+        <v>161.8485099349255</v>
+      </c>
+      <c r="G136" t="n">
+        <v>75790.34889605918</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-9986.116103236451</v>
+      </c>
+      <c r="I136" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="J136" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="L136" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="M136" t="n">
+        <v>242.6084328999027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>7.918119424619969</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>322</v>
+      </c>
+      <c r="B137" t="n">
+        <v>3245</v>
+      </c>
+      <c r="C137" t="n">
+        <v>322</v>
+      </c>
+      <c r="D137" t="n">
+        <v>49.17498151006907</v>
+      </c>
+      <c r="E137" t="n">
+        <v>458.095</v>
+      </c>
+      <c r="F137" t="n">
+        <v>160.7779874775688</v>
+      </c>
+      <c r="G137" t="n">
+        <v>73815.57537967904</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-9771.499180533739</v>
+      </c>
+      <c r="I137" t="n">
+        <v>4.595</v>
+      </c>
+      <c r="J137" t="n">
+        <v>11.705</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L137" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="M137" t="n">
+        <v>238.1128176408108</v>
+      </c>
+      <c r="N137" t="n">
+        <v>7.823376473805849</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>322</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3246</v>
+      </c>
+      <c r="C138" t="n">
+        <v>322</v>
+      </c>
+      <c r="D138" t="n">
+        <v>47.67876451800075</v>
+      </c>
+      <c r="E138" t="n">
+        <v>456.355</v>
+      </c>
+      <c r="F138" t="n">
+        <v>161.3910051901192</v>
+      </c>
+      <c r="G138" t="n">
+        <v>76209.61564505921</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-9880.623166072421</v>
+      </c>
+      <c r="I138" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="J138" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="L138" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M138" t="n">
+        <v>238.1128176408127</v>
+      </c>
+      <c r="N138" t="n">
+        <v>7.907189232523739</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>322</v>
+      </c>
+      <c r="B139" t="n">
+        <v>3247</v>
+      </c>
+      <c r="C139" t="n">
+        <v>322</v>
+      </c>
+      <c r="D139" t="n">
+        <v>47.50250942533923</v>
+      </c>
+      <c r="E139" t="n">
+        <v>455.555</v>
+      </c>
+      <c r="F139" t="n">
+        <v>161.6744238863295</v>
+      </c>
+      <c r="G139" t="n">
+        <v>72918.06711286264</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-9940.990646754948</v>
+      </c>
+      <c r="I139" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="J139" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1.645</v>
+      </c>
+      <c r="L139" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M139" t="n">
+        <v>247.3186373409776</v>
+      </c>
+      <c r="N139" t="n">
+        <v>7.913047927149658</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>323</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3286</v>
+      </c>
+      <c r="C140" t="n">
+        <v>323</v>
+      </c>
+      <c r="D140" t="n">
+        <v>69.74885464038026</v>
+      </c>
+      <c r="E140" t="n">
+        <v>527.955</v>
+      </c>
+      <c r="F140" t="n">
+        <v>139.5035413501849</v>
+      </c>
+      <c r="G140" t="n">
+        <v>78116.00960368689</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-6316.372810807036</v>
+      </c>
+      <c r="I140" t="n">
+        <v>7.285</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="L140" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="M140" t="n">
+        <v>191.2487963113122</v>
+      </c>
+      <c r="N140" t="n">
+        <v>4.321532882127327</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>323</v>
+      </c>
+      <c r="B141" t="n">
+        <v>3287</v>
+      </c>
+      <c r="C141" t="n">
+        <v>323</v>
+      </c>
+      <c r="D141" t="n">
+        <v>70.05705461106128</v>
+      </c>
+      <c r="E141" t="n">
+        <v>529.52</v>
+      </c>
+      <c r="F141" t="n">
+        <v>139.0912376747561</v>
+      </c>
+      <c r="G141" t="n">
+        <v>77275.64291649024</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-6253.225053685826</v>
+      </c>
+      <c r="I141" t="n">
+        <v>7.285</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="L141" t="n">
+        <v>6.035</v>
+      </c>
+      <c r="M141" t="n">
+        <v>188.5892504800049</v>
+      </c>
+      <c r="N141" t="n">
+        <v>4.321558892399789</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>323</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3288</v>
+      </c>
+      <c r="C142" t="n">
+        <v>323</v>
+      </c>
+      <c r="D142" t="n">
+        <v>70.05705461106128</v>
+      </c>
+      <c r="E142" t="n">
+        <v>529.52</v>
+      </c>
+      <c r="F142" t="n">
+        <v>139.0912376747561</v>
+      </c>
+      <c r="G142" t="n">
+        <v>77275.64291649024</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-6253.225053685826</v>
+      </c>
+      <c r="I142" t="n">
+        <v>7.285</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="L142" t="n">
+        <v>6.035</v>
+      </c>
+      <c r="M142" t="n">
+        <v>188.5892504800049</v>
+      </c>
+      <c r="N142" t="n">
+        <v>4.321558892399789</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>323</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3289</v>
+      </c>
+      <c r="C143" t="n">
+        <v>323</v>
+      </c>
+      <c r="D143" t="n">
+        <v>68.67127383456635</v>
+      </c>
+      <c r="E143" t="n">
+        <v>522.4300000000001</v>
+      </c>
+      <c r="F143" t="n">
+        <v>140.9788721427499</v>
+      </c>
+      <c r="G143" t="n">
+        <v>80967.78517635015</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-6527.309348353092</v>
+      </c>
+      <c r="I143" t="n">
+        <v>7.135</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="L143" t="n">
+        <v>5.735</v>
+      </c>
+      <c r="M143" t="n">
+        <v>195.5793957009875</v>
+      </c>
+      <c r="N143" t="n">
+        <v>4.321547192258359</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>323</v>
+      </c>
+      <c r="B144" t="n">
+        <v>3290</v>
+      </c>
+      <c r="C144" t="n">
+        <v>323</v>
+      </c>
+      <c r="D144" t="n">
+        <v>68.67127383456635</v>
+      </c>
+      <c r="E144" t="n">
+        <v>522.4300000000001</v>
+      </c>
+      <c r="F144" t="n">
+        <v>140.9788721427499</v>
+      </c>
+      <c r="G144" t="n">
+        <v>80967.78517635015</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-6527.309348353092</v>
+      </c>
+      <c r="I144" t="n">
+        <v>7.135</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>4.345</v>
+      </c>
+      <c r="L144" t="n">
+        <v>5.735</v>
+      </c>
+      <c r="M144" t="n">
+        <v>195.5793957009875</v>
+      </c>
+      <c r="N144" t="n">
+        <v>4.321547192258359</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>323</v>
+      </c>
+      <c r="B145" t="n">
+        <v>3291</v>
+      </c>
+      <c r="C145" t="n">
+        <v>323</v>
+      </c>
+      <c r="D145" t="n">
+        <v>68.98129174585007</v>
+      </c>
+      <c r="E145" t="n">
+        <v>523.86</v>
+      </c>
+      <c r="F145" t="n">
+        <v>140.5940369059231</v>
+      </c>
+      <c r="G145" t="n">
+        <v>80131.58251956655</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-6462.247334624341</v>
+      </c>
+      <c r="I145" t="n">
+        <v>7.135</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>4.350000000000001</v>
+      </c>
+      <c r="L145" t="n">
+        <v>5.745000000000001</v>
+      </c>
+      <c r="M145" t="n">
+        <v>192.8453458125807</v>
+      </c>
+      <c r="N145" t="n">
+        <v>4.321572535064321</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>323</v>
+      </c>
+      <c r="B146" t="n">
+        <v>3292</v>
+      </c>
+      <c r="C146" t="n">
+        <v>323</v>
+      </c>
+      <c r="D146" t="n">
+        <v>68.98129174585007</v>
+      </c>
+      <c r="E146" t="n">
+        <v>523.86</v>
+      </c>
+      <c r="F146" t="n">
+        <v>140.5940369059231</v>
+      </c>
+      <c r="G146" t="n">
+        <v>80131.58251956655</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-6462.247334624341</v>
+      </c>
+      <c r="I146" t="n">
+        <v>7.135</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>4.350000000000001</v>
+      </c>
+      <c r="L146" t="n">
+        <v>5.745000000000001</v>
+      </c>
+      <c r="M146" t="n">
+        <v>192.8453458125807</v>
+      </c>
+      <c r="N146" t="n">
+        <v>4.321572535064321</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>323</v>
+      </c>
+      <c r="B147" t="n">
+        <v>3293</v>
+      </c>
+      <c r="C147" t="n">
+        <v>323</v>
+      </c>
+      <c r="D147" t="n">
+        <v>69.3210314106506</v>
+      </c>
+      <c r="E147" t="n">
+        <v>525.51</v>
+      </c>
+      <c r="F147" t="n">
+        <v>140.1525987584192</v>
+      </c>
+      <c r="G147" t="n">
+        <v>79219.31286562524</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-6401.573699439072</v>
+      </c>
+      <c r="I147" t="n">
+        <v>7.140000000000001</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>4.355</v>
+      </c>
+      <c r="L147" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M147" t="n">
+        <v>190.0936661727588</v>
+      </c>
+      <c r="N147" t="n">
+        <v>4.32159364778235</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
         <v>325</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B148" t="n">
+        <v>3331</v>
+      </c>
+      <c r="C148" t="n">
+        <v>325</v>
+      </c>
+      <c r="D148" t="n">
+        <v>59.49085720970372</v>
+      </c>
+      <c r="E148" t="n">
+        <v>480.7</v>
+      </c>
+      <c r="F148" t="n">
+        <v>153.21737502296</v>
+      </c>
+      <c r="G148" t="n">
+        <v>82427.4746233732</v>
+      </c>
+      <c r="H148" t="n">
+        <v>-8413.0999302132</v>
+      </c>
+      <c r="I148" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="J148" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="K148" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M148" t="n">
+        <v>224.9750580698667</v>
+      </c>
+      <c r="N148" t="n">
+        <v>6.970510206804811</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>325</v>
+      </c>
+      <c r="B149" t="n">
+        <v>3332</v>
+      </c>
+      <c r="C149" t="n">
+        <v>325</v>
+      </c>
+      <c r="D149" t="n">
+        <v>59.49085720970372</v>
+      </c>
+      <c r="E149" t="n">
+        <v>480.7</v>
+      </c>
+      <c r="F149" t="n">
+        <v>153.21737502296</v>
+      </c>
+      <c r="G149" t="n">
+        <v>85669.64200844093</v>
+      </c>
+      <c r="H149" t="n">
+        <v>-8413.0999302132</v>
+      </c>
+      <c r="I149" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="J149" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="K149" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L149" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M149" t="n">
+        <v>224.9750580698667</v>
+      </c>
+      <c r="N149" t="n">
+        <v>6.970510206804811</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>325</v>
+      </c>
+      <c r="B150" t="n">
+        <v>3333</v>
+      </c>
+      <c r="C150" t="n">
+        <v>325</v>
+      </c>
+      <c r="D150" t="n">
+        <v>60.07681334224453</v>
+      </c>
+      <c r="E150" t="n">
+        <v>482.105</v>
+      </c>
+      <c r="F150" t="n">
+        <v>152.7708531824745</v>
+      </c>
+      <c r="G150" t="n">
+        <v>82388.79197475422</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-8341.358994065151</v>
+      </c>
+      <c r="I150" t="n">
+        <v>5.205</v>
+      </c>
+      <c r="J150" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="K150" t="n">
+        <v>2.505000000000001</v>
+      </c>
+      <c r="L150" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="M150" t="n">
+        <v>221.2319672436798</v>
+      </c>
+      <c r="N150" t="n">
+        <v>7.045283876208701</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>325</v>
+      </c>
+      <c r="B151" t="n">
+        <v>3334</v>
+      </c>
+      <c r="C151" t="n">
+        <v>325</v>
+      </c>
+      <c r="D151" t="n">
+        <v>60.07681334224453</v>
+      </c>
+      <c r="E151" t="n">
+        <v>482.105</v>
+      </c>
+      <c r="F151" t="n">
+        <v>152.7708531824745</v>
+      </c>
+      <c r="G151" t="n">
+        <v>85566.02214318189</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-8341.358994065151</v>
+      </c>
+      <c r="I151" t="n">
+        <v>5.205</v>
+      </c>
+      <c r="J151" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="K151" t="n">
+        <v>2.505000000000001</v>
+      </c>
+      <c r="L151" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="M151" t="n">
+        <v>221.2319672436798</v>
+      </c>
+      <c r="N151" t="n">
+        <v>7.045283876208701</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>325</v>
+      </c>
+      <c r="B152" t="n">
+        <v>3335</v>
+      </c>
+      <c r="C152" t="n">
+        <v>325</v>
+      </c>
+      <c r="D152" t="n">
+        <v>60.70810056580181</v>
+      </c>
+      <c r="E152" t="n">
+        <v>483.735</v>
+      </c>
+      <c r="F152" t="n">
+        <v>152.2560744488963</v>
+      </c>
+      <c r="G152" t="n">
+        <v>82276.54722715581</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-8277.649528251537</v>
+      </c>
+      <c r="I152" t="n">
+        <v>5.175</v>
+      </c>
+      <c r="J152" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="K152" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L152" t="n">
+        <v>3.395</v>
+      </c>
+      <c r="M152" t="n">
+        <v>217.5153677353537</v>
+      </c>
+      <c r="N152" t="n">
+        <v>7.120034056730911</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>325</v>
+      </c>
+      <c r="B153" t="n">
+        <v>3336</v>
+      </c>
+      <c r="C153" t="n">
+        <v>325</v>
+      </c>
+      <c r="D153" t="n">
+        <v>60.70810056580181</v>
+      </c>
+      <c r="E153" t="n">
+        <v>483.735</v>
+      </c>
+      <c r="F153" t="n">
+        <v>152.2560744488963</v>
+      </c>
+      <c r="G153" t="n">
+        <v>85296.69238101688</v>
+      </c>
+      <c r="H153" t="n">
+        <v>-8277.649528251537</v>
+      </c>
+      <c r="I153" t="n">
+        <v>5.175</v>
+      </c>
+      <c r="J153" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="K153" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L153" t="n">
+        <v>3.395</v>
+      </c>
+      <c r="M153" t="n">
+        <v>217.5153677353537</v>
+      </c>
+      <c r="N153" t="n">
+        <v>7.120034056730911</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>325</v>
+      </c>
+      <c r="B154" t="n">
+        <v>3337</v>
+      </c>
+      <c r="C154" t="n">
+        <v>325</v>
+      </c>
+      <c r="D154" t="n">
+        <v>58.71376252322056</v>
+      </c>
+      <c r="E154" t="n">
+        <v>479.23</v>
+      </c>
+      <c r="F154" t="n">
+        <v>153.6873571636518</v>
+      </c>
+      <c r="G154" t="n">
+        <v>81891.42168438996</v>
+      </c>
+      <c r="H154" t="n">
+        <v>-8480.898199442736</v>
+      </c>
+      <c r="I154" t="n">
+        <v>5.175</v>
+      </c>
+      <c r="J154" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="K154" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="L154" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M154" t="n">
+        <v>225.333710165379</v>
+      </c>
+      <c r="N154" t="n">
+        <v>6.970276077183139</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>325</v>
+      </c>
+      <c r="B155" t="n">
+        <v>3338</v>
+      </c>
+      <c r="C155" t="n">
+        <v>325</v>
+      </c>
+      <c r="D155" t="n">
+        <v>58.71376252322056</v>
+      </c>
+      <c r="E155" t="n">
+        <v>479.23</v>
+      </c>
+      <c r="F155" t="n">
+        <v>153.6873571636518</v>
+      </c>
+      <c r="G155" t="n">
+        <v>85142.67575812041</v>
+      </c>
+      <c r="H155" t="n">
+        <v>-8480.898199442736</v>
+      </c>
+      <c r="I155" t="n">
+        <v>5.175</v>
+      </c>
+      <c r="J155" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="K155" t="n">
+        <v>2.435</v>
+      </c>
+      <c r="L155" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M155" t="n">
+        <v>225.333710165379</v>
+      </c>
+      <c r="N155" t="n">
+        <v>6.970276077183139</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>325</v>
+      </c>
+      <c r="B156" t="n">
+        <v>3339</v>
+      </c>
+      <c r="C156" t="n">
+        <v>325</v>
+      </c>
+      <c r="D156" t="n">
+        <v>59.37082968538485</v>
+      </c>
+      <c r="E156" t="n">
+        <v>480.64</v>
+      </c>
+      <c r="F156" t="n">
+        <v>153.2365016926117</v>
+      </c>
+      <c r="G156" t="n">
+        <v>81850.6230975658</v>
+      </c>
+      <c r="H156" t="n">
+        <v>-8418.330910705699</v>
+      </c>
+      <c r="I156" t="n">
+        <v>5.145</v>
+      </c>
+      <c r="J156" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="K156" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L156" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="M156" t="n">
+        <v>221.5131610596042</v>
+      </c>
+      <c r="N156" t="n">
+        <v>7.045067755689094</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>325</v>
+      </c>
+      <c r="B157" t="n">
+        <v>3340</v>
+      </c>
+      <c r="C157" t="n">
+        <v>325</v>
+      </c>
+      <c r="D157" t="n">
+        <v>59.37082968538485</v>
+      </c>
+      <c r="E157" t="n">
+        <v>480.64</v>
+      </c>
+      <c r="F157" t="n">
+        <v>153.2365016926117</v>
+      </c>
+      <c r="G157" t="n">
+        <v>85024.20360029639</v>
+      </c>
+      <c r="H157" t="n">
+        <v>-8418.330910705699</v>
+      </c>
+      <c r="I157" t="n">
+        <v>5.145</v>
+      </c>
+      <c r="J157" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="K157" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L157" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="M157" t="n">
+        <v>221.5131610596042</v>
+      </c>
+      <c r="N157" t="n">
+        <v>7.045067755689094</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>325</v>
+      </c>
+      <c r="B158" t="n">
         <v>3341</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C158" t="n">
         <v>325</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D158" t="n">
         <v>60.01714583172794</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E158" t="n">
         <v>482.345</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F158" t="n">
         <v>152.6948391162692</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G158" t="n">
         <v>81787.82577264791</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H158" t="n">
         <v>-8343.767232546861</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I158" t="n">
         <v>5.115</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J158" t="n">
         <v>19.375</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K158" t="n">
         <v>2.430000000000001</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L158" t="n">
         <v>3.3</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M158" t="n">
         <v>217.7253288156539</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N158" t="n">
         <v>7.119832755100101</v>
       </c>
     </row>
